--- a/test/Extract Thermo-calc Results-Melting Range/Al-Cu-Li_COST/melting_range.xlsx
+++ b/test/Extract Thermo-calc Results-Melting Range/Al-Cu-Li_COST/melting_range.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="457">
   <si>
     <t>File</t>
   </si>
@@ -190,6 +190,9 @@
     <t>Al0.020Cu0.035Li_np-T.exp</t>
   </si>
   <si>
+    <t>Al0.020Cu0.040Li_np-T.exp</t>
+  </si>
+  <si>
     <t>Al0.020Cu0.045Li_np-T.exp</t>
   </si>
   <si>
@@ -607,6 +610,9 @@
     <t>Al0.085Cu0.020Li_np-T.exp</t>
   </si>
   <si>
+    <t>Al0.085Cu0.025Li_np-T.exp</t>
+  </si>
+  <si>
     <t>Al0.085Cu0.030Li_np-T.exp</t>
   </si>
   <si>
@@ -1067,6 +1073,9 @@
   </si>
   <si>
     <t>Al0.155Cu0.025Li_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.155Cu0.030Li_np-T.exp</t>
   </si>
   <si>
     <t>Al0.155Cu0.035Li_np-T.exp</t>
@@ -1733,7 +1742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F449"/>
+  <dimension ref="A1:F452"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1767,13 +1776,13 @@
         <v>0.005</v>
       </c>
       <c r="D2">
-        <v>934.12734391</v>
+        <v>934.12480536</v>
       </c>
       <c r="E2">
-        <v>934.12596434</v>
+        <v>934.101821</v>
       </c>
       <c r="F2">
-        <v>0.001379570000040076</v>
+        <v>0.02298436000000947</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1787,13 +1796,13 @@
         <v>0.01</v>
       </c>
       <c r="D3">
-        <v>933.4564832</v>
+        <v>933.45403616</v>
       </c>
       <c r="E3">
-        <v>933.04939895</v>
+        <v>933.0269492899999</v>
       </c>
       <c r="F3">
-        <v>0.4070842500000253</v>
+        <v>0.4270868700000392</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1807,13 +1816,13 @@
         <v>0.015</v>
       </c>
       <c r="D4">
-        <v>931.94224605</v>
+        <v>931.93988992</v>
       </c>
       <c r="E4">
-        <v>929.84735562</v>
+        <v>929.82603597</v>
       </c>
       <c r="F4">
-        <v>2.094890429999964</v>
+        <v>2.113853950000021</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1827,13 +1836,13 @@
         <v>0.02</v>
       </c>
       <c r="D5">
-        <v>929.83647681</v>
+        <v>929.83419119</v>
       </c>
       <c r="E5">
-        <v>924.24534099</v>
+        <v>924.2252588</v>
       </c>
       <c r="F5">
-        <v>5.591135819999977</v>
+        <v>5.60893238999995</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1847,13 +1856,13 @@
         <v>0.025</v>
       </c>
       <c r="D6">
-        <v>927.26074498</v>
+        <v>927.25849884</v>
       </c>
       <c r="E6">
-        <v>916.31075607</v>
+        <v>916.29254616</v>
       </c>
       <c r="F6">
-        <v>10.94998891</v>
+        <v>10.96595267999999</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1867,13 +1876,13 @@
         <v>0.03</v>
       </c>
       <c r="D7">
-        <v>924.26509017</v>
+        <v>924.26284863</v>
       </c>
       <c r="E7">
-        <v>906.41456156</v>
+        <v>906.3988412800001</v>
       </c>
       <c r="F7">
-        <v>17.85052860999997</v>
+        <v>17.86400734999995</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1887,13 +1896,13 @@
         <v>0.035</v>
       </c>
       <c r="D8">
-        <v>920.86264934</v>
+        <v>920.86037727</v>
       </c>
       <c r="E8">
-        <v>894.99730571</v>
+        <v>894.98434179</v>
       </c>
       <c r="F8">
-        <v>25.86534362999998</v>
+        <v>25.87603547999993</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1907,13 +1916,13 @@
         <v>0.04</v>
       </c>
       <c r="D9">
-        <v>917.04952945</v>
+        <v>917.04719363</v>
       </c>
       <c r="E9">
-        <v>882.42570481</v>
+        <v>882.4154328</v>
       </c>
       <c r="F9">
-        <v>34.62382464000007</v>
+        <v>34.63176083000008</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1927,13 +1936,13 @@
         <v>0.045</v>
       </c>
       <c r="D10">
-        <v>912.81583818</v>
+        <v>912.81340855</v>
       </c>
       <c r="E10">
-        <v>868.97189702</v>
+        <v>868.96405262</v>
       </c>
       <c r="F10">
-        <v>43.84394115999999</v>
+        <v>43.84935593</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1947,13 +1956,13 @@
         <v>0.05</v>
       </c>
       <c r="D11">
-        <v>908.15148254</v>
+        <v>908.14893265</v>
       </c>
       <c r="E11">
-        <v>868.8096700999999</v>
+        <v>868.80242017</v>
       </c>
       <c r="F11">
-        <v>39.34181244000001</v>
+        <v>39.34651248</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1967,13 +1976,13 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>932.17345692</v>
+        <v>932.17660286</v>
       </c>
       <c r="E12">
-        <v>920.21164571</v>
+        <v>920.21790708</v>
       </c>
       <c r="F12">
-        <v>11.96181121000006</v>
+        <v>11.95869577999997</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1987,13 +1996,13 @@
         <v>0.005</v>
       </c>
       <c r="D13">
-        <v>932.81199828</v>
+        <v>932.8560719</v>
       </c>
       <c r="E13">
-        <v>915.19725183</v>
+        <v>922.2692218</v>
       </c>
       <c r="F13">
-        <v>17.61474644999998</v>
+        <v>10.58685009999999</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2007,13 +2016,13 @@
         <v>0.01</v>
       </c>
       <c r="D14">
-        <v>932.1777296400001</v>
+        <v>932.23053766</v>
       </c>
       <c r="E14">
-        <v>904.42062145</v>
+        <v>922.1045114999999</v>
       </c>
       <c r="F14">
-        <v>27.75710819000005</v>
+        <v>10.12602616000004</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2027,13 +2036,13 @@
         <v>0.015</v>
       </c>
       <c r="D15">
-        <v>930.71945432</v>
+        <v>930.76059494</v>
       </c>
       <c r="E15">
-        <v>886.8812019</v>
+        <v>919.59635328</v>
       </c>
       <c r="F15">
-        <v>43.83825242</v>
+        <v>11.16424166000002</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2047,13 +2056,13 @@
         <v>0.02</v>
       </c>
       <c r="D16">
-        <v>928.6700732199999</v>
+        <v>928.68854597</v>
       </c>
       <c r="E16">
-        <v>864.44306212</v>
+        <v>914.76630928</v>
       </c>
       <c r="F16">
-        <v>64.22701109999991</v>
+        <v>13.92223668999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2067,13 +2076,13 @@
         <v>0.025</v>
       </c>
       <c r="D17">
-        <v>926.14036771</v>
+        <v>926.13099705</v>
       </c>
       <c r="E17">
-        <v>838.83481451</v>
+        <v>907.84449962</v>
       </c>
       <c r="F17">
-        <v>87.30555319999996</v>
+        <v>18.28649743000005</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2087,13 +2096,13 @@
         <v>0.03</v>
       </c>
       <c r="D18">
-        <v>923.17485935</v>
+        <v>923.13605934</v>
       </c>
       <c r="E18">
-        <v>810.65304626</v>
+        <v>899.15727801</v>
       </c>
       <c r="F18">
-        <v>112.52181309</v>
+        <v>23.97878132999995</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2107,13 +2116,13 @@
         <v>0.035</v>
       </c>
       <c r="D19">
-        <v>919.7844113899999</v>
+        <v>919.71679939</v>
       </c>
       <c r="E19">
-        <v>812.50372009</v>
+        <v>889.012288</v>
       </c>
       <c r="F19">
-        <v>107.2806912999999</v>
+        <v>30.70451138999999</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2127,13 +2136,13 @@
         <v>0.04</v>
       </c>
       <c r="D20">
-        <v>915.96479736</v>
+        <v>915.870344</v>
       </c>
       <c r="E20">
-        <v>813.95224774</v>
+        <v>877.66190972</v>
       </c>
       <c r="F20">
-        <v>102.0125496200001</v>
+        <v>38.20843428000001</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2147,13 +2156,13 @@
         <v>0.045</v>
       </c>
       <c r="D21">
-        <v>911.70690419</v>
+        <v>911.58841497</v>
       </c>
       <c r="E21">
-        <v>813.95224774</v>
+        <v>865.48585443</v>
       </c>
       <c r="F21">
-        <v>97.75465645000008</v>
+        <v>46.10256054000001</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2167,13 +2176,13 @@
         <v>0.05</v>
       </c>
       <c r="D22">
-        <v>907.00199958</v>
+        <v>906.86281707</v>
       </c>
       <c r="E22">
-        <v>813.95224774</v>
+        <v>865.36569131</v>
       </c>
       <c r="F22">
-        <v>93.04975184</v>
+        <v>41.49712576000002</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2187,13 +2196,13 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>933.47299846</v>
+        <v>933.47352686</v>
       </c>
       <c r="E23">
-        <v>933.47299845</v>
+        <v>933.44862385</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>0.02490301000000272</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2207,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>930.8705347699999</v>
+        <v>930.87370476</v>
       </c>
       <c r="E24">
-        <v>907.395209</v>
+        <v>907.40507585</v>
       </c>
       <c r="F24">
-        <v>23.47532576999993</v>
+        <v>23.46862891000001</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2227,13 +2236,13 @@
         <v>0.005</v>
       </c>
       <c r="D25">
-        <v>931.49739207</v>
+        <v>931.58126426</v>
       </c>
       <c r="E25">
-        <v>895.28715863</v>
+        <v>910.9403785</v>
       </c>
       <c r="F25">
-        <v>36.21023344000002</v>
+        <v>20.64088576000006</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2247,13 +2256,13 @@
         <v>0.01</v>
       </c>
       <c r="D26">
-        <v>930.90017997</v>
+        <v>930.99926562</v>
       </c>
       <c r="E26">
-        <v>873.33814202</v>
+        <v>911.83775026</v>
       </c>
       <c r="F26">
-        <v>57.56203794999999</v>
+        <v>19.16151535999995</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2267,13 +2276,13 @@
         <v>0.015</v>
       </c>
       <c r="D27">
-        <v>929.4964162</v>
+        <v>929.57122792</v>
       </c>
       <c r="E27">
-        <v>844.8168226</v>
+        <v>910.24466261</v>
       </c>
       <c r="F27">
-        <v>84.67959359999998</v>
+        <v>19.32656530999998</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2287,13 +2296,13 @@
         <v>0.02</v>
       </c>
       <c r="D28">
-        <v>927.5006084</v>
+        <v>927.53000044</v>
       </c>
       <c r="E28">
-        <v>813.13061427</v>
+        <v>906.37459417</v>
       </c>
       <c r="F28">
-        <v>114.36999413</v>
+        <v>21.15540626999996</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2307,13 +2316,13 @@
         <v>0.025</v>
       </c>
       <c r="D29">
-        <v>925.01330478</v>
+        <v>924.98749164</v>
       </c>
       <c r="E29">
-        <v>798.70156802</v>
+        <v>900.50686787</v>
       </c>
       <c r="F29">
-        <v>126.31173676</v>
+        <v>24.48062377000008</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2327,13 +2336,13 @@
         <v>0.03</v>
       </c>
       <c r="D30">
-        <v>922.0738843</v>
+        <v>921.9900780299999</v>
       </c>
       <c r="E30">
-        <v>806.50036288</v>
+        <v>892.92173593</v>
       </c>
       <c r="F30">
-        <v>115.57352142</v>
+        <v>29.0683421</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2347,13 +2356,13 @@
         <v>0.035</v>
       </c>
       <c r="D31">
-        <v>918.69118541</v>
+        <v>918.55089591</v>
       </c>
       <c r="E31">
-        <v>811.7631923599999</v>
+        <v>883.8616265000001</v>
       </c>
       <c r="F31">
-        <v>106.9279930500001</v>
+        <v>34.68926940999995</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2367,13 +2376,13 @@
         <v>0.04</v>
       </c>
       <c r="D32">
-        <v>914.86081591</v>
+        <v>914.668193</v>
       </c>
       <c r="E32">
-        <v>813.95224774</v>
+        <v>873.5279322599999</v>
       </c>
       <c r="F32">
-        <v>100.9085681700001</v>
+        <v>41.14026074000003</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2387,13 +2396,13 @@
         <v>0.045</v>
       </c>
       <c r="D33">
-        <v>910.57454221</v>
+        <v>910.3353796</v>
       </c>
       <c r="E33">
-        <v>813.95224774</v>
+        <v>862.4677272599999</v>
       </c>
       <c r="F33">
-        <v>96.62229447000004</v>
+        <v>47.86765234000006</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2407,13 +2416,13 @@
         <v>0.05</v>
       </c>
       <c r="D34">
-        <v>905.82505721</v>
+        <v>905.5462176</v>
       </c>
       <c r="E34">
-        <v>813.95224775</v>
+        <v>862.24943415</v>
       </c>
       <c r="F34">
-        <v>91.87280945999998</v>
+        <v>43.29678345000002</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2427,13 +2436,13 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>929.5637547600001</v>
+        <v>929.56695007</v>
       </c>
       <c r="E35">
-        <v>895.12777901</v>
+        <v>895.14146423</v>
       </c>
       <c r="F35">
-        <v>34.43597575000001</v>
+        <v>34.42548583999996</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2447,13 +2456,13 @@
         <v>0.005</v>
       </c>
       <c r="D36">
-        <v>930.18285092</v>
+        <v>930.30233387</v>
       </c>
       <c r="E36">
-        <v>875.11462441</v>
+        <v>900.27077274</v>
       </c>
       <c r="F36">
-        <v>55.06822650999993</v>
+        <v>30.03156113</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2467,13 +2476,13 @@
         <v>0.01</v>
       </c>
       <c r="D37">
-        <v>929.62328442</v>
+        <v>929.7622534</v>
       </c>
       <c r="E37">
-        <v>844.05908774</v>
+        <v>902.36615803</v>
       </c>
       <c r="F37">
-        <v>85.56419668000001</v>
+        <v>27.39609537000001</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2487,13 +2496,13 @@
         <v>0.015</v>
       </c>
       <c r="D38">
-        <v>928.27247636</v>
+        <v>928.37365819</v>
       </c>
       <c r="E38">
-        <v>808.79173572</v>
+        <v>901.8163275000001</v>
       </c>
       <c r="F38">
-        <v>119.48074064</v>
+        <v>26.55733068999996</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2507,13 +2516,13 @@
         <v>0.02</v>
       </c>
       <c r="D39">
-        <v>926.32734794</v>
+        <v>926.36030098</v>
       </c>
       <c r="E39">
-        <v>786.7444322600001</v>
+        <v>898.9579635600001</v>
       </c>
       <c r="F39">
-        <v>139.5829156799999</v>
+        <v>27.40233741999998</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2527,13 +2536,13 @@
         <v>0.025</v>
       </c>
       <c r="D40">
-        <v>923.87876193</v>
+        <v>923.8296569300001</v>
       </c>
       <c r="E40">
-        <v>796.4425685800001</v>
+        <v>894.09587928</v>
       </c>
       <c r="F40">
-        <v>127.4361933499999</v>
+        <v>29.73377765000009</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2547,13 +2556,13 @@
         <v>0.03</v>
       </c>
       <c r="D41">
-        <v>920.9613242299999</v>
+        <v>920.82656022</v>
       </c>
       <c r="E41">
-        <v>804.97098554</v>
+        <v>887.49216438</v>
       </c>
       <c r="F41">
-        <v>115.9903386899999</v>
+        <v>33.33439584000007</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2567,13 +2576,13 @@
         <v>0.035</v>
       </c>
       <c r="D42">
-        <v>917.58209707</v>
+        <v>917.36435647</v>
       </c>
       <c r="E42">
-        <v>810.89017957</v>
+        <v>879.36391808</v>
       </c>
       <c r="F42">
-        <v>106.6919175</v>
+        <v>38.00043839</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2587,13 +2596,13 @@
         <v>0.04</v>
       </c>
       <c r="D43">
-        <v>913.73668095</v>
+        <v>913.44251586</v>
       </c>
       <c r="E43">
-        <v>813.95224774</v>
+        <v>869.89190835</v>
       </c>
       <c r="F43">
-        <v>99.78443321000009</v>
+        <v>43.55060750999996</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2607,13 +2616,13 @@
         <v>0.045</v>
       </c>
       <c r="D44">
-        <v>909.41782333</v>
+        <v>909.05621307</v>
       </c>
       <c r="E44">
-        <v>813.95224774</v>
+        <v>859.71516667</v>
       </c>
       <c r="F44">
-        <v>95.46557559000007</v>
+        <v>49.34104639999998</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2627,13 +2636,13 @@
         <v>0.05</v>
       </c>
       <c r="D45">
-        <v>904.61970428</v>
+        <v>904.20122444</v>
       </c>
       <c r="E45">
-        <v>813.95224774</v>
+        <v>859.41651015</v>
       </c>
       <c r="F45">
-        <v>90.66745653999999</v>
+        <v>44.78471429000001</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2647,13 +2656,13 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>928.2529037</v>
+        <v>928.25612532</v>
       </c>
       <c r="E46">
-        <v>883.51009384</v>
+        <v>883.52783089</v>
       </c>
       <c r="F46">
-        <v>44.74280986000008</v>
+        <v>44.72829443000001</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2667,13 +2676,13 @@
         <v>0.005</v>
       </c>
       <c r="D47">
-        <v>928.86795872</v>
+        <v>929.01894806</v>
       </c>
       <c r="E47">
-        <v>855.73021453</v>
+        <v>890.35158716</v>
       </c>
       <c r="F47">
-        <v>73.13774419000003</v>
+        <v>38.66736089999995</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2687,13 +2696,13 @@
         <v>0.01</v>
       </c>
       <c r="D48">
-        <v>928.34648319</v>
+        <v>928.51907865</v>
       </c>
       <c r="E48">
-        <v>818.11588579</v>
+        <v>893.72553524</v>
       </c>
       <c r="F48">
-        <v>110.2305974</v>
+        <v>34.79354340999998</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2707,13 +2716,13 @@
         <v>0.015</v>
       </c>
       <c r="D49">
-        <v>927.04696856</v>
+        <v>927.16738983</v>
       </c>
       <c r="E49">
-        <v>784.07366308</v>
+        <v>894.25777095</v>
       </c>
       <c r="F49">
-        <v>142.97330548</v>
+        <v>32.90961888000004</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2727,13 +2736,13 @@
         <v>0.02</v>
       </c>
       <c r="D50">
-        <v>925.14954648</v>
+        <v>925.17890112</v>
       </c>
       <c r="E50">
-        <v>786.65528284</v>
+        <v>892.38655633</v>
       </c>
       <c r="F50">
-        <v>138.49426364</v>
+        <v>32.79234479000002</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2747,13 +2756,13 @@
         <v>0.025</v>
       </c>
       <c r="D51">
-        <v>922.73593375</v>
+        <v>922.65691507</v>
       </c>
       <c r="E51">
-        <v>793.95639131</v>
+        <v>888.4496417300001</v>
       </c>
       <c r="F51">
-        <v>128.77954244</v>
+        <v>34.20727333999992</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2767,13 +2776,13 @@
         <v>0.03</v>
       </c>
       <c r="D52">
-        <v>919.83632819</v>
+        <v>919.64491603</v>
       </c>
       <c r="E52">
-        <v>803.24924276</v>
+        <v>882.71370768</v>
       </c>
       <c r="F52">
-        <v>116.58708543</v>
+        <v>36.93120835000002</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2787,13 +2796,13 @@
         <v>0.035</v>
       </c>
       <c r="D53">
-        <v>916.45625811</v>
+        <v>916.15659883</v>
       </c>
       <c r="E53">
-        <v>809.87049199</v>
+        <v>875.39210567</v>
       </c>
       <c r="F53">
-        <v>106.58576612</v>
+        <v>40.76449316000003</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2804,16 +2813,16 @@
         <v>0.02</v>
       </c>
       <c r="C54">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D54">
-        <v>908.23580593</v>
+        <v>912.19275771</v>
       </c>
       <c r="E54">
-        <v>813.95224774</v>
+        <v>866.66021461</v>
       </c>
       <c r="F54">
-        <v>94.28355819000001</v>
+        <v>45.5325431</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2824,16 +2833,16 @@
         <v>0.02</v>
       </c>
       <c r="C55">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D55">
-        <v>903.38497882</v>
+        <v>907.75040734</v>
       </c>
       <c r="E55">
-        <v>813.95224774</v>
+        <v>857.19535937</v>
       </c>
       <c r="F55">
-        <v>89.43273108000005</v>
+        <v>50.55504797000003</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2841,19 +2850,19 @@
         <v>60</v>
       </c>
       <c r="B56">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D56">
-        <v>926.93776016</v>
+        <v>902.82740319</v>
       </c>
       <c r="E56">
-        <v>872.62434529</v>
+        <v>856.83083054</v>
       </c>
       <c r="F56">
-        <v>54.31341487000009</v>
+        <v>45.99657265000008</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2864,16 +2873,16 @@
         <v>0.025</v>
       </c>
       <c r="C57">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>927.55229078</v>
+        <v>926.94100885</v>
       </c>
       <c r="E57">
-        <v>837.82471856</v>
+        <v>872.64631664</v>
       </c>
       <c r="F57">
-        <v>89.72757222000007</v>
+        <v>54.29469220999999</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2884,16 +2893,16 @@
         <v>0.025</v>
       </c>
       <c r="C58">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D58">
-        <v>927.06920632</v>
+        <v>927.7307698</v>
       </c>
       <c r="E58">
-        <v>795.57137342</v>
+        <v>881.2238208799999</v>
       </c>
       <c r="F58">
-        <v>131.4978329</v>
+        <v>46.50694892000001</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2904,16 +2913,16 @@
         <v>0.025</v>
       </c>
       <c r="C59">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D59">
-        <v>925.81921687</v>
+        <v>927.26930677</v>
       </c>
       <c r="E59">
-        <v>783.72612727</v>
+        <v>885.8939258299999</v>
       </c>
       <c r="F59">
-        <v>142.0930896</v>
+        <v>41.37538094000001</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2924,16 +2933,16 @@
         <v>0.025</v>
       </c>
       <c r="C60">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D60">
-        <v>923.9664477</v>
+        <v>925.95191857</v>
       </c>
       <c r="E60">
-        <v>786.55222869</v>
+        <v>887.48592464</v>
       </c>
       <c r="F60">
-        <v>137.41421901</v>
+        <v>38.46599392999997</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2944,16 +2953,16 @@
         <v>0.025</v>
       </c>
       <c r="C61">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D61">
-        <v>921.58400407</v>
+        <v>923.98524647</v>
       </c>
       <c r="E61">
-        <v>791.22978188</v>
+        <v>886.54099263</v>
       </c>
       <c r="F61">
-        <v>130.35422219</v>
+        <v>37.44425383999999</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2964,16 +2973,16 @@
         <v>0.025</v>
       </c>
       <c r="C62">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D62">
-        <v>918.69803304</v>
+        <v>921.46868313</v>
       </c>
       <c r="E62">
-        <v>801.31783082</v>
+        <v>883.44115902</v>
       </c>
       <c r="F62">
-        <v>117.38020222</v>
+        <v>38.02752411000006</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2984,16 +2993,16 @@
         <v>0.025</v>
       </c>
       <c r="C63">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D63">
-        <v>915.31276882</v>
+        <v>918.4445535999999</v>
       </c>
       <c r="E63">
-        <v>808.68847291</v>
+        <v>878.47157023</v>
       </c>
       <c r="F63">
-        <v>106.62429591</v>
+        <v>39.97298336999995</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -3004,16 +3013,16 @@
         <v>0.025</v>
       </c>
       <c r="C64">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D64">
-        <v>911.4242660800001</v>
+        <v>914.9270418999999</v>
       </c>
       <c r="E64">
-        <v>813.20912799</v>
+        <v>871.85308442</v>
       </c>
       <c r="F64">
-        <v>98.2151380900001</v>
+        <v>43.07395747999999</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3024,16 +3033,16 @@
         <v>0.025</v>
       </c>
       <c r="C65">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D65">
-        <v>907.02753579</v>
+        <v>910.91836847</v>
       </c>
       <c r="E65">
-        <v>813.95224774</v>
+        <v>863.76346426</v>
       </c>
       <c r="F65">
-        <v>93.07528805000004</v>
+        <v>47.15490421000004</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -3044,16 +3053,16 @@
         <v>0.025</v>
       </c>
       <c r="C66">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D66">
-        <v>902.11990501</v>
+        <v>906.41746769</v>
       </c>
       <c r="E66">
-        <v>813.95224774</v>
+        <v>854.88088233</v>
       </c>
       <c r="F66">
-        <v>88.16765727000006</v>
+        <v>51.53658536</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -3061,19 +3070,19 @@
         <v>71</v>
       </c>
       <c r="B67">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D67">
-        <v>925.61809286</v>
+        <v>901.42433796</v>
       </c>
       <c r="E67">
-        <v>862.52527691</v>
+        <v>854.4623804399999</v>
       </c>
       <c r="F67">
-        <v>63.09281595000004</v>
+        <v>46.96195752000006</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -3084,16 +3093,16 @@
         <v>0.03</v>
       </c>
       <c r="C68">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>926.2354126499999</v>
+        <v>925.62136907</v>
       </c>
       <c r="E68">
-        <v>821.6583783999999</v>
+        <v>862.55155597</v>
       </c>
       <c r="F68">
-        <v>104.57703425</v>
+        <v>63.06981310000003</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -3104,16 +3113,16 @@
         <v>0.03</v>
       </c>
       <c r="C69">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D69">
-        <v>925.79087359</v>
+        <v>926.4374493</v>
       </c>
       <c r="E69">
-        <v>779.8212625899999</v>
+        <v>872.8862556</v>
       </c>
       <c r="F69">
-        <v>145.9696110000001</v>
+        <v>53.5511937</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3124,16 +3133,16 @@
         <v>0.03</v>
       </c>
       <c r="C70">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D70">
-        <v>924.58853322</v>
+        <v>926.0124954200001</v>
       </c>
       <c r="E70">
-        <v>783.347563</v>
+        <v>878.81885444</v>
       </c>
       <c r="F70">
-        <v>141.24097022</v>
+        <v>47.19364098000005</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -3144,16 +3153,16 @@
         <v>0.03</v>
       </c>
       <c r="C71">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D71">
-        <v>922.77728399</v>
+        <v>924.72673016</v>
       </c>
       <c r="E71">
-        <v>786.43413126</v>
+        <v>881.41304823</v>
       </c>
       <c r="F71">
-        <v>136.34315273</v>
+        <v>43.31368193000003</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3164,16 +3173,16 @@
         <v>0.03</v>
       </c>
       <c r="C72">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D72">
-        <v>920.42214323</v>
+        <v>922.77877515</v>
       </c>
       <c r="E72">
-        <v>788.25130301</v>
+        <v>881.31893958</v>
       </c>
       <c r="F72">
-        <v>132.1708402199999</v>
+        <v>41.45983557</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -3184,16 +3193,16 @@
         <v>0.03</v>
       </c>
       <c r="C73">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D73">
-        <v>917.54556381</v>
+        <v>920.26437188</v>
       </c>
       <c r="E73">
-        <v>799.1587039999999</v>
+        <v>878.97039407</v>
       </c>
       <c r="F73">
-        <v>118.38685981</v>
+        <v>41.29397781</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3204,16 +3213,16 @@
         <v>0.03</v>
       </c>
       <c r="C74">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D74">
-        <v>914.15071763</v>
+        <v>917.22487859</v>
       </c>
       <c r="E74">
-        <v>807.32691187</v>
+        <v>874.67820499</v>
       </c>
       <c r="F74">
-        <v>106.82380576</v>
+        <v>42.54667359999996</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -3224,16 +3233,16 @@
         <v>0.03</v>
       </c>
       <c r="C75">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D75">
-        <v>910.23411586</v>
+        <v>913.6751067500001</v>
       </c>
       <c r="E75">
-        <v>812.53915777</v>
+        <v>868.67625015</v>
       </c>
       <c r="F75">
-        <v>97.69495809</v>
+        <v>44.99885660000007</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3244,16 +3253,16 @@
         <v>0.03</v>
       </c>
       <c r="C76">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D76">
-        <v>905.79204531</v>
+        <v>909.61880697</v>
       </c>
       <c r="E76">
-        <v>813.95224774</v>
+        <v>861.14853842</v>
       </c>
       <c r="F76">
-        <v>91.83979757000009</v>
+        <v>48.47026855000001</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3264,16 +3273,16 @@
         <v>0.03</v>
       </c>
       <c r="C77">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D77">
-        <v>900.82349356</v>
+        <v>905.0569146399999</v>
       </c>
       <c r="E77">
-        <v>813.95224774</v>
+        <v>852.74846655</v>
       </c>
       <c r="F77">
-        <v>86.87124582000001</v>
+        <v>52.30844808999996</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3281,19 +3290,19 @@
         <v>82</v>
       </c>
       <c r="B78">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D78">
-        <v>924.2936628800001</v>
+        <v>899.99163924</v>
       </c>
       <c r="E78">
-        <v>853.2384092</v>
+        <v>852.28580778</v>
       </c>
       <c r="F78">
-        <v>71.05525368000008</v>
+        <v>47.70583146000001</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3304,16 +3313,16 @@
         <v>0.035</v>
       </c>
       <c r="C79">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>924.9168803</v>
+        <v>924.29696682</v>
       </c>
       <c r="E79">
-        <v>807.24470116</v>
+        <v>853.26893479</v>
       </c>
       <c r="F79">
-        <v>117.67217914</v>
+        <v>71.02803202999996</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3324,16 +3333,16 @@
         <v>0.035</v>
       </c>
       <c r="C80">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D80">
-        <v>924.51089437</v>
+        <v>925.13862781</v>
       </c>
       <c r="E80">
-        <v>779.90744152</v>
+        <v>865.3094256099999</v>
       </c>
       <c r="F80">
-        <v>144.6034528499999</v>
+        <v>59.82920220000005</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3344,16 +3353,16 @@
         <v>0.035</v>
       </c>
       <c r="C81">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D81">
-        <v>923.35421947</v>
+        <v>924.74819208</v>
       </c>
       <c r="E81">
-        <v>782.9355369899999</v>
+        <v>872.43586467</v>
       </c>
       <c r="F81">
-        <v>140.41868248</v>
+        <v>52.31232740999997</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3364,16 +3373,16 @@
         <v>0.035</v>
       </c>
       <c r="C82">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D82">
-        <v>921.58127667</v>
+        <v>923.49130413</v>
       </c>
       <c r="E82">
-        <v>786.29974892</v>
+        <v>875.95693345</v>
       </c>
       <c r="F82">
-        <v>135.28152775</v>
+        <v>47.53437068000005</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3384,16 +3393,16 @@
         <v>0.035</v>
       </c>
       <c r="C83">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D83">
-        <v>919.24951288</v>
+        <v>921.55891824</v>
       </c>
       <c r="E83">
-        <v>786.77612263</v>
+        <v>876.63462889</v>
       </c>
       <c r="F83">
-        <v>132.47339025</v>
+        <v>44.92428934999998</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3404,16 +3413,16 @@
         <v>0.035</v>
       </c>
       <c r="C84">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D84">
-        <v>916.37803357</v>
+        <v>919.04338824</v>
       </c>
       <c r="E84">
-        <v>796.75347114</v>
+        <v>874.9576324</v>
       </c>
       <c r="F84">
-        <v>119.62456243</v>
+        <v>44.08575584000005</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3424,16 +3433,16 @@
         <v>0.035</v>
       </c>
       <c r="C85">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D85">
-        <v>912.96917927</v>
+        <v>915.98529523</v>
       </c>
       <c r="E85">
-        <v>805.7669957000001</v>
+        <v>871.26522986</v>
       </c>
       <c r="F85">
-        <v>107.20218357</v>
+        <v>44.72006537000004</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3444,16 +3453,16 @@
         <v>0.035</v>
       </c>
       <c r="C86">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D86">
-        <v>909.02006775</v>
+        <v>912.40021809</v>
       </c>
       <c r="E86">
-        <v>811.72531428</v>
+        <v>865.8066017</v>
       </c>
       <c r="F86">
-        <v>97.29475346999993</v>
+        <v>46.59361638999997</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3464,16 +3473,16 @@
         <v>0.035</v>
       </c>
       <c r="C87">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D87">
-        <v>904.52835361</v>
+        <v>908.2935422100001</v>
       </c>
       <c r="E87">
-        <v>813.95224774</v>
+        <v>858.773726</v>
       </c>
       <c r="F87">
-        <v>90.57610586999999</v>
+        <v>49.51981621000004</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3484,16 +3493,16 @@
         <v>0.035</v>
       </c>
       <c r="C88">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D88">
-        <v>899.49474133</v>
+        <v>903.66828682</v>
       </c>
       <c r="E88">
-        <v>813.95224774</v>
+        <v>850.77815055</v>
       </c>
       <c r="F88">
-        <v>85.54249359000005</v>
+        <v>52.89013627000008</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3501,19 +3510,19 @@
         <v>93</v>
       </c>
       <c r="B89">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D89">
-        <v>922.96422146</v>
+        <v>898.52894587</v>
       </c>
       <c r="E89">
-        <v>844.76335787</v>
+        <v>850.27945167</v>
       </c>
       <c r="F89">
-        <v>78.20086358999993</v>
+        <v>48.24949420000007</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3524,16 +3533,16 @@
         <v>0.04</v>
       </c>
       <c r="C90">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>923.59623992</v>
+        <v>922.96755324</v>
       </c>
       <c r="E90">
-        <v>794.48413434</v>
+        <v>844.79793913</v>
       </c>
       <c r="F90">
-        <v>129.11210558</v>
+        <v>78.16961411</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3544,16 +3553,16 @@
         <v>0.04</v>
       </c>
       <c r="C91">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D91">
-        <v>923.2286675</v>
+        <v>923.83393661</v>
       </c>
       <c r="E91">
-        <v>779.99520737</v>
+        <v>858.44798668</v>
       </c>
       <c r="F91">
-        <v>143.23346013</v>
+        <v>65.38594993000004</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3564,16 +3573,16 @@
         <v>0.04</v>
       </c>
       <c r="C92">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D92">
-        <v>922.11556627</v>
+        <v>923.47593432</v>
       </c>
       <c r="E92">
-        <v>782.487423</v>
+        <v>866.67868843</v>
       </c>
       <c r="F92">
-        <v>139.62814327</v>
+        <v>56.79724589</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3584,16 +3593,16 @@
         <v>0.04</v>
       </c>
       <c r="C93">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D93">
-        <v>920.3776355</v>
+        <v>922.24510721</v>
       </c>
       <c r="E93">
-        <v>786.14772649</v>
+        <v>871.0442072</v>
       </c>
       <c r="F93">
-        <v>134.22990901</v>
+        <v>51.20090001000005</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3604,16 +3613,16 @@
         <v>0.04</v>
       </c>
       <c r="C94">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D94">
-        <v>918.06526113</v>
+        <v>920.32509886</v>
       </c>
       <c r="E94">
-        <v>786.77612263</v>
+        <v>872.41651694</v>
       </c>
       <c r="F94">
-        <v>131.2891384999999</v>
+        <v>47.90858192000007</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3624,16 +3633,16 @@
         <v>0.04</v>
       </c>
       <c r="C95">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D95">
-        <v>915.19454324</v>
+        <v>917.80513449</v>
       </c>
       <c r="E95">
-        <v>794.08400607</v>
+        <v>871.33851295</v>
       </c>
       <c r="F95">
-        <v>121.11053717</v>
+        <v>46.46662154000001</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3644,16 +3653,16 @@
         <v>0.04</v>
       </c>
       <c r="C96">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D96">
-        <v>911.76721728</v>
+        <v>914.72520701</v>
       </c>
       <c r="E96">
-        <v>803.98832201</v>
+        <v>868.1781489799999</v>
       </c>
       <c r="F96">
-        <v>107.7788952699999</v>
+        <v>46.54705803000002</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3664,16 +3673,16 @@
         <v>0.04</v>
       </c>
       <c r="C97">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D97">
-        <v>907.7811536200001</v>
+        <v>911.10180399</v>
       </c>
       <c r="E97">
-        <v>810.7505555499999</v>
+        <v>863.20035477</v>
       </c>
       <c r="F97">
-        <v>97.03059807000011</v>
+        <v>47.90144922000002</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3684,16 +3693,16 @@
         <v>0.04</v>
       </c>
       <c r="C98">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D98">
-        <v>903.23546614</v>
+        <v>906.94205343</v>
       </c>
       <c r="E98">
-        <v>813.95224774</v>
+        <v>856.6055969499999</v>
       </c>
       <c r="F98">
-        <v>89.28321840000001</v>
+        <v>50.33645648000004</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3704,16 +3713,16 @@
         <v>0.04</v>
       </c>
       <c r="C99">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D99">
-        <v>898.1326304200001</v>
+        <v>902.25114371</v>
       </c>
       <c r="E99">
-        <v>813.95224774</v>
+        <v>848.9526705</v>
       </c>
       <c r="F99">
-        <v>84.18038268000009</v>
+        <v>53.29847321</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3721,19 +3730,19 @@
         <v>104</v>
       </c>
       <c r="B100">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D100">
-        <v>921.6295102300001</v>
+        <v>897.03593015</v>
       </c>
       <c r="E100">
-        <v>837.07947476</v>
+        <v>848.42465373</v>
       </c>
       <c r="F100">
-        <v>84.55003547000001</v>
+        <v>48.61127641999997</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3744,16 +3753,16 @@
         <v>0.045</v>
       </c>
       <c r="C101">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>922.27302768</v>
+        <v>921.6328691799999</v>
       </c>
       <c r="E101">
-        <v>789.65741512</v>
+        <v>837.1178163</v>
       </c>
       <c r="F101">
-        <v>132.61561256</v>
+        <v>84.51505287999998</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3764,16 +3773,16 @@
         <v>0.045</v>
       </c>
       <c r="C102">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D102">
-        <v>921.9435816599999</v>
+        <v>922.52299713</v>
       </c>
       <c r="E102">
-        <v>780.08460183</v>
+        <v>852.24935387</v>
       </c>
       <c r="F102">
-        <v>141.85897983</v>
+        <v>70.27364325999997</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3784,16 +3793,16 @@
         <v>0.045</v>
       </c>
       <c r="C103">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D103">
-        <v>920.87185306</v>
+        <v>922.19525021</v>
       </c>
       <c r="E103">
-        <v>782.00039213</v>
+        <v>861.4841373100001</v>
       </c>
       <c r="F103">
-        <v>138.87146093</v>
+        <v>60.71111289999999</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3804,16 +3813,16 @@
         <v>0.045</v>
       </c>
       <c r="C104">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D104">
-        <v>919.1655586000001</v>
+        <v>920.98759985</v>
       </c>
       <c r="E104">
-        <v>785.9765836399999</v>
+        <v>866.61071063</v>
       </c>
       <c r="F104">
-        <v>133.1889749600001</v>
+        <v>54.37688922000007</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3824,16 +3833,16 @@
         <v>0.045</v>
       </c>
       <c r="C105">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D105">
-        <v>916.86852442</v>
+        <v>919.07673422</v>
       </c>
       <c r="E105">
-        <v>786.77612263</v>
+        <v>868.60478168</v>
       </c>
       <c r="F105">
-        <v>130.0924017899999</v>
+        <v>50.47195254000007</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3844,16 +3853,16 @@
         <v>0.045</v>
       </c>
       <c r="C106">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D106">
-        <v>913.99418128</v>
+        <v>916.54900846</v>
       </c>
       <c r="E106">
-        <v>791.13335194</v>
+        <v>868.06040265</v>
       </c>
       <c r="F106">
-        <v>122.86082934</v>
+        <v>48.48860580999997</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3864,16 +3873,16 @@
         <v>0.045</v>
       </c>
       <c r="C107">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D107">
-        <v>910.54388185</v>
+        <v>913.44401729</v>
       </c>
       <c r="E107">
-        <v>801.9690167799999</v>
+        <v>865.37278993</v>
       </c>
       <c r="F107">
-        <v>108.5748650700001</v>
+        <v>48.07122736000008</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3884,16 +3893,16 @@
         <v>0.045</v>
       </c>
       <c r="C108">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D108">
-        <v>906.51639178</v>
+        <v>909.77930056</v>
       </c>
       <c r="E108">
-        <v>809.5958419999999</v>
+        <v>860.82202788</v>
       </c>
       <c r="F108">
-        <v>96.9205497800001</v>
+        <v>48.95727268000007</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3904,16 +3913,16 @@
         <v>0.045</v>
       </c>
       <c r="C109">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D109">
-        <v>901.91237449</v>
+        <v>905.5638347</v>
       </c>
       <c r="E109">
-        <v>813.88035143</v>
+        <v>854.61690392</v>
       </c>
       <c r="F109">
-        <v>88.03202306000003</v>
+        <v>50.94693078</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3924,16 +3933,16 @@
         <v>0.045</v>
       </c>
       <c r="C110">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D110">
-        <v>896.73613185</v>
+        <v>900.80506899</v>
       </c>
       <c r="E110">
-        <v>813.95224775</v>
+        <v>847.25700441</v>
       </c>
       <c r="F110">
-        <v>82.78388410000002</v>
+        <v>53.54806457999996</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3941,19 +3950,19 @@
         <v>115</v>
       </c>
       <c r="B111">
+        <v>0.045</v>
+      </c>
+      <c r="C111">
         <v>0.05</v>
       </c>
-      <c r="C111">
-        <v>0</v>
-      </c>
       <c r="D111">
-        <v>920.28926116</v>
+        <v>895.51230169</v>
       </c>
       <c r="E111">
-        <v>830.15178335</v>
+        <v>846.7052425099999</v>
       </c>
       <c r="F111">
-        <v>90.13747781000006</v>
+        <v>48.80705918000001</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3964,16 +3973,16 @@
         <v>0.05</v>
       </c>
       <c r="C112">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>920.9467695</v>
+        <v>920.29264684</v>
       </c>
       <c r="E112">
-        <v>789.3797095899999</v>
+        <v>830.19351741</v>
       </c>
       <c r="F112">
-        <v>131.56705991</v>
+        <v>90.09912942999995</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3984,16 +3993,16 @@
         <v>0.05</v>
       </c>
       <c r="C113">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D113">
-        <v>920.65501268</v>
+        <v>921.20541943</v>
       </c>
       <c r="E113">
-        <v>780.17566841</v>
+        <v>846.65904368</v>
       </c>
       <c r="F113">
-        <v>140.4793442700001</v>
+        <v>74.54637575000004</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4004,16 +4013,16 @@
         <v>0.05</v>
       </c>
       <c r="C114">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D114">
-        <v>919.62234772</v>
+        <v>920.9056564</v>
       </c>
       <c r="E114">
-        <v>781.4714057</v>
+        <v>856.79411973</v>
       </c>
       <c r="F114">
-        <v>138.15094202</v>
+        <v>64.11153666999996</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4024,16 +4033,16 @@
         <v>0.05</v>
       </c>
       <c r="C115">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D115">
-        <v>917.9442325700001</v>
+        <v>919.71823289</v>
       </c>
       <c r="E115">
-        <v>785.78470213</v>
+        <v>862.6007939900001</v>
       </c>
       <c r="F115">
-        <v>132.15953044</v>
+        <v>57.11743889999991</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4044,16 +4053,16 @@
         <v>0.05</v>
       </c>
       <c r="C116">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D116">
-        <v>915.65842706</v>
+        <v>917.81323458</v>
       </c>
       <c r="E116">
-        <v>786.77612263</v>
+        <v>865.14912121</v>
       </c>
       <c r="F116">
-        <v>128.88230443</v>
+        <v>52.66411337</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4064,16 +4073,16 @@
         <v>0.05</v>
       </c>
       <c r="C117">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D117">
-        <v>912.7760237700001</v>
+        <v>915.27440471</v>
       </c>
       <c r="E117">
-        <v>787.8869938399999</v>
+        <v>865.07974414</v>
       </c>
       <c r="F117">
-        <v>124.8890299300001</v>
+        <v>50.19466057</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4084,16 +4093,16 @@
         <v>0.05</v>
       </c>
       <c r="C118">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D118">
-        <v>909.29820978</v>
+        <v>912.1411338200001</v>
       </c>
       <c r="E118">
-        <v>799.6860037599999</v>
+        <v>862.81282908</v>
       </c>
       <c r="F118">
-        <v>109.61220602</v>
+        <v>49.32830474000002</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4104,16 +4113,16 @@
         <v>0.05</v>
       </c>
       <c r="C119">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D119">
-        <v>905.22478691</v>
+        <v>908.43215014</v>
       </c>
       <c r="E119">
-        <v>808.23997152</v>
+        <v>858.64243714</v>
       </c>
       <c r="F119">
-        <v>96.98481538999999</v>
+        <v>49.78971300000001</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4124,16 +4133,16 @@
         <v>0.05</v>
       </c>
       <c r="C120">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D120">
-        <v>900.55805604</v>
+        <v>904.15839626</v>
       </c>
       <c r="E120">
-        <v>813.3090008200001</v>
+        <v>852.7851252</v>
       </c>
       <c r="F120">
-        <v>87.24905521999995</v>
+        <v>51.37327105999998</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4144,16 +4153,16 @@
         <v>0.05</v>
       </c>
       <c r="C121">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D121">
-        <v>895.30419741</v>
+        <v>899.32967408</v>
       </c>
       <c r="E121">
-        <v>813.95224774</v>
+        <v>845.67801449</v>
       </c>
       <c r="F121">
-        <v>81.35194967000007</v>
+        <v>53.65165959000001</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4161,19 +4170,19 @@
         <v>126</v>
       </c>
       <c r="B122">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D122">
-        <v>918.94319617</v>
+        <v>893.95781345</v>
       </c>
       <c r="E122">
-        <v>823.93616783</v>
+        <v>845.10712826</v>
       </c>
       <c r="F122">
-        <v>95.00702833999992</v>
+        <v>48.85068519000004</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -4184,16 +4193,16 @@
         <v>0.055</v>
       </c>
       <c r="C123">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>919.61698086</v>
+        <v>918.9466077</v>
       </c>
       <c r="E123">
-        <v>789.09706954</v>
+        <v>823.98088565</v>
       </c>
       <c r="F123">
-        <v>130.51991132</v>
+        <v>94.96572204999995</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4204,16 +4213,16 @@
         <v>0.055</v>
       </c>
       <c r="C124">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D124">
-        <v>919.3623282</v>
+        <v>919.88080445</v>
       </c>
       <c r="E124">
-        <v>780.26845141</v>
+        <v>841.6237215899999</v>
       </c>
       <c r="F124">
-        <v>139.09387679</v>
+        <v>78.25708286000008</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4224,16 +4233,16 @@
         <v>0.055</v>
       </c>
       <c r="C125">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D125">
-        <v>918.36630697</v>
+        <v>919.60666154</v>
       </c>
       <c r="E125">
-        <v>780.8972112500001</v>
+        <v>852.55621555</v>
       </c>
       <c r="F125">
-        <v>137.4690957199999</v>
+        <v>67.05044598999996</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4244,16 +4253,16 @@
         <v>0.055</v>
       </c>
       <c r="C126">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D126">
-        <v>916.7128319</v>
+        <v>918.43644884</v>
       </c>
       <c r="E126">
-        <v>785.5703117100001</v>
+        <v>858.96627688</v>
       </c>
       <c r="F126">
-        <v>131.1425201899999</v>
+        <v>59.47017196000002</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4264,16 +4273,16 @@
         <v>0.055</v>
       </c>
       <c r="C127">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D127">
-        <v>914.43408101</v>
+        <v>916.53400369</v>
       </c>
       <c r="E127">
-        <v>786.77612263</v>
+        <v>862.00696643</v>
       </c>
       <c r="F127">
-        <v>127.65795838</v>
+        <v>54.52703725999993</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4284,16 +4293,16 @@
         <v>0.055</v>
       </c>
       <c r="C128">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D128">
-        <v>911.5391332</v>
+        <v>913.98071611</v>
       </c>
       <c r="E128">
-        <v>786.77612263</v>
+        <v>862.36010627</v>
       </c>
       <c r="F128">
-        <v>124.76301057</v>
+        <v>51.62060984000004</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4304,16 +4313,16 @@
         <v>0.055</v>
       </c>
       <c r="C129">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D129">
-        <v>908.0292242</v>
+        <v>910.81596155</v>
       </c>
       <c r="E129">
-        <v>797.1155175599999</v>
+        <v>860.4680229099999</v>
       </c>
       <c r="F129">
-        <v>110.9137066400001</v>
+        <v>50.34793864000005</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4324,16 +4333,16 @@
         <v>0.055</v>
       </c>
       <c r="C130">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D130">
-        <v>903.90533013</v>
+        <v>907.05980554</v>
       </c>
       <c r="E130">
-        <v>806.6594507900001</v>
+        <v>856.6372738699999</v>
       </c>
       <c r="F130">
-        <v>97.24587933999999</v>
+        <v>50.42253167000001</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4344,16 +4353,16 @@
         <v>0.055</v>
       </c>
       <c r="C131">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D131">
-        <v>899.1714737</v>
+        <v>902.72526795</v>
       </c>
       <c r="E131">
-        <v>812.58197106</v>
+        <v>851.09142251</v>
       </c>
       <c r="F131">
-        <v>86.58950263999998</v>
+        <v>51.63384543999996</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4364,16 +4373,16 @@
         <v>0.055</v>
       </c>
       <c r="C132">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D132">
-        <v>893.8357664</v>
+        <v>897.82460249</v>
       </c>
       <c r="E132">
-        <v>813.95224774</v>
+        <v>844.20416885</v>
       </c>
       <c r="F132">
-        <v>79.88351866000005</v>
+        <v>53.62043363999999</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4381,19 +4390,19 @@
         <v>137</v>
       </c>
       <c r="B133">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D133">
-        <v>917.59102721</v>
+        <v>892.37226481</v>
       </c>
       <c r="E133">
-        <v>820.74106208</v>
+        <v>843.61799209</v>
       </c>
       <c r="F133">
-        <v>96.84996512999999</v>
+        <v>48.75427272000002</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4404,16 +4413,16 @@
         <v>0.06</v>
       </c>
       <c r="C134">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>918.28316623</v>
+        <v>917.59446343</v>
       </c>
       <c r="E134">
-        <v>788.80936181</v>
+        <v>820.7272612199999</v>
       </c>
       <c r="F134">
-        <v>129.47380442</v>
+        <v>96.86720221000007</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4424,16 +4433,16 @@
         <v>0.06</v>
       </c>
       <c r="C135">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D135">
-        <v>918.0648830600001</v>
+        <v>918.5487418</v>
       </c>
       <c r="E135">
-        <v>780.3629967000001</v>
+        <v>837.09280799</v>
       </c>
       <c r="F135">
-        <v>137.70188636</v>
+        <v>81.45593381000003</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4444,16 +4453,16 @@
         <v>0.06</v>
       </c>
       <c r="C136">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D136">
-        <v>917.10297581</v>
+        <v>918.29776229</v>
       </c>
       <c r="E136">
-        <v>780.27434403</v>
+        <v>848.72355547</v>
       </c>
       <c r="F136">
-        <v>136.82863178</v>
+        <v>69.57420682000009</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4464,16 +4473,16 @@
         <v>0.06</v>
       </c>
       <c r="C137">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D137">
-        <v>915.47051901</v>
+        <v>917.14168138</v>
       </c>
       <c r="E137">
-        <v>785.33147472</v>
+        <v>855.6653881</v>
       </c>
       <c r="F137">
-        <v>130.13904429</v>
+        <v>61.47629328000005</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4484,16 +4493,16 @@
         <v>0.06</v>
       </c>
       <c r="C138">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D138">
-        <v>913.1945862</v>
+        <v>915.23843934</v>
       </c>
       <c r="E138">
-        <v>786.77612263</v>
+        <v>859.14204265</v>
       </c>
       <c r="F138">
-        <v>126.41846357</v>
+        <v>56.09639669000001</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4504,16 +4513,16 @@
         <v>0.06</v>
       </c>
       <c r="C139">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D139">
-        <v>910.28255949</v>
+        <v>912.66733343</v>
       </c>
       <c r="E139">
-        <v>786.77612263</v>
+        <v>859.87072381</v>
       </c>
       <c r="F139">
-        <v>123.50643686</v>
+        <v>52.79660962000003</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4524,16 +4533,16 @@
         <v>0.06</v>
       </c>
       <c r="C140">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D140">
-        <v>906.73593526</v>
+        <v>909.46791253</v>
       </c>
       <c r="E140">
-        <v>794.23394243</v>
+        <v>858.3129216</v>
       </c>
       <c r="F140">
-        <v>112.5019928300001</v>
+        <v>51.15499093000005</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4544,16 +4553,16 @@
         <v>0.06</v>
       </c>
       <c r="C141">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D141">
-        <v>902.55699669</v>
+        <v>905.6617309</v>
       </c>
       <c r="E141">
-        <v>804.82844309</v>
+        <v>854.78607054</v>
       </c>
       <c r="F141">
-        <v>97.72855360000005</v>
+        <v>50.87566035999998</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4564,16 +4573,16 @@
         <v>0.06</v>
       </c>
       <c r="C142">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D142">
-        <v>897.7515757800001</v>
+        <v>901.26400052</v>
       </c>
       <c r="E142">
-        <v>811.67868215</v>
+        <v>849.51987811</v>
       </c>
       <c r="F142">
-        <v>86.07289363000007</v>
+        <v>51.74412240999993</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4584,16 +4593,16 @@
         <v>0.06</v>
       </c>
       <c r="C143">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D143">
-        <v>892.32976369</v>
+        <v>896.28953416</v>
       </c>
       <c r="E143">
-        <v>813.95224774</v>
+        <v>843.55546156</v>
       </c>
       <c r="F143">
-        <v>78.37751595000009</v>
+        <v>52.73407259999999</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4601,19 +4610,19 @@
         <v>148</v>
       </c>
       <c r="B144">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D144">
-        <v>916.23245548</v>
+        <v>890.75551346</v>
       </c>
       <c r="E144">
-        <v>820.74106227</v>
+        <v>843.48960233</v>
       </c>
       <c r="F144">
-        <v>95.49139320999996</v>
+        <v>47.26591112999995</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4624,16 +4633,16 @@
         <v>0.065</v>
       </c>
       <c r="C145">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D145">
-        <v>916.94482134</v>
+        <v>916.23591497</v>
       </c>
       <c r="E145">
-        <v>788.51644835</v>
+        <v>820.72711079</v>
       </c>
       <c r="F145">
-        <v>128.42837299</v>
+        <v>95.50880417999997</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4644,16 +4653,16 @@
         <v>0.065</v>
       </c>
       <c r="C146">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D146">
-        <v>916.76202096</v>
+        <v>917.20881023</v>
       </c>
       <c r="E146">
-        <v>780.45935159</v>
+        <v>833.01922372</v>
       </c>
       <c r="F146">
-        <v>136.30266937</v>
+        <v>84.18958651000003</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4664,16 +4673,16 @@
         <v>0.065</v>
       </c>
       <c r="C147">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D147">
-        <v>915.83158725</v>
+        <v>916.9784464000001</v>
       </c>
       <c r="E147">
-        <v>779.5991360100001</v>
+        <v>845.2544185100001</v>
       </c>
       <c r="F147">
-        <v>136.2324512399999</v>
+        <v>71.72402789</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4684,16 +4693,16 @@
         <v>0.065</v>
       </c>
       <c r="C148">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D148">
-        <v>914.21644403</v>
+        <v>915.83335546</v>
       </c>
       <c r="E148">
-        <v>785.06606916</v>
+        <v>852.6618151599999</v>
       </c>
       <c r="F148">
-        <v>129.1503748700001</v>
+        <v>63.17154030000006</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4704,16 +4713,16 @@
         <v>0.065</v>
       </c>
       <c r="C149">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D149">
-        <v>911.93902731</v>
+        <v>913.92593428</v>
       </c>
       <c r="E149">
-        <v>786.77612263</v>
+        <v>856.52323443</v>
       </c>
       <c r="F149">
-        <v>125.16290468</v>
+        <v>57.40269984999998</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4724,16 +4733,16 @@
         <v>0.065</v>
       </c>
       <c r="C150">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D150">
-        <v>909.00533996</v>
+        <v>911.33364376</v>
       </c>
       <c r="E150">
-        <v>786.77612263</v>
+        <v>857.5853934</v>
       </c>
       <c r="F150">
-        <v>122.22921733</v>
+        <v>53.74825035999993</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4744,16 +4753,16 @@
         <v>0.065</v>
       </c>
       <c r="C151">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D151">
-        <v>905.41733866</v>
+        <v>908.09640629</v>
       </c>
       <c r="E151">
-        <v>791.01912077</v>
+        <v>856.32590783</v>
       </c>
       <c r="F151">
-        <v>114.3982178900001</v>
+        <v>51.77049846</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4764,16 +4773,16 @@
         <v>0.065</v>
       </c>
       <c r="C152">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D152">
-        <v>901.17874968</v>
+        <v>904.23740463</v>
       </c>
       <c r="E152">
-        <v>802.7188497</v>
+        <v>853.07143597</v>
       </c>
       <c r="F152">
-        <v>98.45989998000005</v>
+        <v>51.16596865999998</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4784,16 +4793,16 @@
         <v>0.065</v>
       </c>
       <c r="C153">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D153">
-        <v>896.29729548</v>
+        <v>899.77417298</v>
       </c>
       <c r="E153">
-        <v>810.57580764</v>
+        <v>848.0569238099999</v>
       </c>
       <c r="F153">
-        <v>85.72148784000001</v>
+        <v>51.71724917000006</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4804,16 +4813,16 @@
         <v>0.065</v>
       </c>
       <c r="C154">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D154">
-        <v>890.78509777</v>
+        <v>894.72419089</v>
       </c>
       <c r="E154">
-        <v>813.95224774</v>
+        <v>843.69882145</v>
       </c>
       <c r="F154">
-        <v>76.83285003000003</v>
+        <v>51.02536944000008</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -4821,19 +4830,19 @@
         <v>159</v>
       </c>
       <c r="B155">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D155">
-        <v>914.8671715200001</v>
+        <v>889.10747731</v>
       </c>
       <c r="E155">
-        <v>820.74106227</v>
+        <v>843.48960234</v>
       </c>
       <c r="F155">
-        <v>94.12610925000001</v>
+        <v>45.61787497</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -4844,16 +4853,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C156">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>915.60142752</v>
+        <v>914.87065255</v>
       </c>
       <c r="E156">
-        <v>788.2181859900001</v>
+        <v>820.72695659</v>
       </c>
       <c r="F156">
-        <v>127.38324153</v>
+        <v>94.14369596000006</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4864,16 +4873,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C157">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D157">
-        <v>915.4530741</v>
+        <v>915.86057753</v>
       </c>
       <c r="E157">
-        <v>780.55756497</v>
+        <v>829.35964184</v>
       </c>
       <c r="F157">
-        <v>134.8955091299999</v>
+        <v>86.50093569000001</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4884,16 +4893,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C158">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D158">
-        <v>914.55136214</v>
+        <v>915.64819063</v>
       </c>
       <c r="E158">
-        <v>778.86773514</v>
+        <v>842.1117123499999</v>
       </c>
       <c r="F158">
-        <v>135.683627</v>
+        <v>73.5364782800001</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -4904,16 +4913,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C159">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D159">
-        <v>912.94974456</v>
+        <v>914.51088828</v>
       </c>
       <c r="E159">
-        <v>784.7717705</v>
+        <v>849.92387575</v>
       </c>
       <c r="F159">
-        <v>128.17797406</v>
+        <v>64.58701253000004</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4924,16 +4933,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C160">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D160">
-        <v>910.66648006</v>
+        <v>912.59587635</v>
       </c>
       <c r="E160">
-        <v>786.77612263</v>
+        <v>854.12368417</v>
       </c>
       <c r="F160">
-        <v>123.89035743</v>
+        <v>58.47219217999998</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -4944,16 +4953,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C161">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D161">
-        <v>907.7064956299999</v>
+        <v>909.97903836</v>
       </c>
       <c r="E161">
-        <v>786.77612263</v>
+        <v>855.48162662</v>
       </c>
       <c r="F161">
-        <v>120.9303729999999</v>
+        <v>54.49741173999996</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4964,16 +4973,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C162">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D162">
-        <v>904.07241595</v>
+        <v>906.70086416</v>
       </c>
       <c r="E162">
-        <v>787.45225114</v>
+        <v>854.48847031</v>
       </c>
       <c r="F162">
-        <v>116.62016481</v>
+        <v>52.21239385000001</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4984,16 +4993,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C163">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D163">
-        <v>899.7695359000001</v>
+        <v>902.78632213</v>
       </c>
       <c r="E163">
-        <v>800.30061339</v>
+        <v>851.47846864</v>
       </c>
       <c r="F163">
-        <v>99.46892251000008</v>
+        <v>51.30785349000007</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5004,16 +5013,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C164">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D164">
-        <v>894.8075506500001</v>
+        <v>898.25539273</v>
       </c>
       <c r="E164">
-        <v>809.24697215</v>
+        <v>846.69090675</v>
       </c>
       <c r="F164">
-        <v>85.56057850000002</v>
+        <v>51.56448598000009</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -5024,16 +5033,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C165">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D165">
-        <v>889.20066177</v>
+        <v>893.12834265</v>
       </c>
       <c r="E165">
-        <v>813.95224774</v>
+        <v>843.7838791200001</v>
       </c>
       <c r="F165">
-        <v>75.24841403000005</v>
+        <v>49.34446352999998</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5041,19 +5050,19 @@
         <v>170</v>
       </c>
       <c r="B166">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D166">
-        <v>913.49485483</v>
+        <v>887.42814571</v>
       </c>
       <c r="E166">
-        <v>820.74106227</v>
+        <v>843.48960234</v>
       </c>
       <c r="F166">
-        <v>92.75379255999997</v>
+        <v>43.93854336999993</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5064,16 +5073,16 @@
         <v>0.075</v>
       </c>
       <c r="C167">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D167">
-        <v>914.25245706</v>
+        <v>913.4983554200001</v>
       </c>
       <c r="E167">
-        <v>787.91442618</v>
+        <v>820.72679945</v>
       </c>
       <c r="F167">
-        <v>126.33803088</v>
+        <v>92.77155597000001</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5084,16 +5093,16 @@
         <v>0.075</v>
       </c>
       <c r="C168">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D168">
-        <v>914.13736277</v>
+        <v>914.5036003</v>
       </c>
       <c r="E168">
-        <v>780.65768689</v>
+        <v>826.07446449</v>
       </c>
       <c r="F168">
-        <v>133.4796758799999</v>
+        <v>88.42913581000005</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5104,16 +5113,16 @@
         <v>0.075</v>
       </c>
       <c r="C169">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D169">
-        <v>913.26151022</v>
+        <v>914.30646173</v>
       </c>
       <c r="E169">
-        <v>778.4033752</v>
+        <v>839.2624550199999</v>
       </c>
       <c r="F169">
-        <v>134.85813502</v>
+        <v>75.04400671000008</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -5124,16 +5133,16 @@
         <v>0.075</v>
       </c>
       <c r="C170">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D170">
-        <v>911.66954546</v>
+        <v>913.1736886</v>
       </c>
       <c r="E170">
-        <v>784.44603195</v>
+        <v>847.4238208199999</v>
       </c>
       <c r="F170">
-        <v>127.22351351</v>
+        <v>65.74986778000005</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -5144,16 +5153,16 @@
         <v>0.075</v>
       </c>
       <c r="C171">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D171">
-        <v>909.37600347</v>
+        <v>911.2476471799999</v>
       </c>
       <c r="E171">
-        <v>786.77612263</v>
+        <v>851.92007375</v>
       </c>
       <c r="F171">
-        <v>122.59988084</v>
+        <v>59.32757342999992</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -5164,16 +5173,16 @@
         <v>0.075</v>
       </c>
       <c r="C172">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D172">
-        <v>906.3850371</v>
+        <v>908.60290699</v>
       </c>
       <c r="E172">
-        <v>786.77612263</v>
+        <v>853.53999171</v>
       </c>
       <c r="F172">
-        <v>119.6089144699999</v>
+        <v>55.06291527999997</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -5184,16 +5193,16 @@
         <v>0.075</v>
       </c>
       <c r="C173">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D173">
-        <v>902.70013419</v>
+        <v>905.28072</v>
       </c>
       <c r="E173">
-        <v>786.77612263</v>
+        <v>852.78464404</v>
       </c>
       <c r="F173">
-        <v>115.9240115599999</v>
+        <v>52.49607595999998</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -5204,16 +5213,16 @@
         <v>0.075</v>
       </c>
       <c r="C174">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D174">
-        <v>898.32828738</v>
+        <v>901.30799776</v>
       </c>
       <c r="E174">
-        <v>797.54236779</v>
+        <v>849.9943132</v>
       </c>
       <c r="F174">
-        <v>100.78591959</v>
+        <v>51.31368456000007</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -5224,16 +5233,16 @@
         <v>0.075</v>
       </c>
       <c r="C175">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D175">
-        <v>893.2812439</v>
+        <v>896.70730254</v>
       </c>
       <c r="E175">
-        <v>807.66247925</v>
+        <v>845.41175218</v>
       </c>
       <c r="F175">
-        <v>85.61876465</v>
+        <v>51.29555035999999</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -5244,16 +5253,16 @@
         <v>0.075</v>
       </c>
       <c r="C176">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D176">
-        <v>887.57533297</v>
+        <v>891.50181177</v>
       </c>
       <c r="E176">
-        <v>813.42862293</v>
+        <v>843.80958787</v>
       </c>
       <c r="F176">
-        <v>74.14671004000002</v>
+        <v>47.69222390000004</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -5261,19 +5270,19 @@
         <v>181</v>
       </c>
       <c r="B177">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D177">
-        <v>912.11517365</v>
+        <v>885.717588</v>
       </c>
       <c r="E177">
-        <v>820.74106227</v>
+        <v>843.48960234</v>
       </c>
       <c r="F177">
-        <v>91.37411137999993</v>
+        <v>42.22798565999994</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -5284,16 +5293,16 @@
         <v>0.08</v>
       </c>
       <c r="C178">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D178">
-        <v>912.89737043</v>
+        <v>912.11869151</v>
       </c>
       <c r="E178">
-        <v>787.60501475</v>
+        <v>820.72663851</v>
       </c>
       <c r="F178">
-        <v>125.29235568</v>
+        <v>91.39205299999992</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -5304,16 +5313,16 @@
         <v>0.08</v>
       </c>
       <c r="C179">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D179">
-        <v>912.8141960200001</v>
+        <v>913.1374237799999</v>
       </c>
       <c r="E179">
-        <v>780.75976918</v>
+        <v>823.1276546399999</v>
       </c>
       <c r="F179">
-        <v>132.05442684</v>
+        <v>90.00976914</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -5324,16 +5333,16 @@
         <v>0.08</v>
       </c>
       <c r="C180">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D180">
-        <v>911.96122622</v>
+        <v>912.95271615</v>
       </c>
       <c r="E180">
-        <v>778.4033752</v>
+        <v>836.67728454</v>
       </c>
       <c r="F180">
-        <v>133.5578510199999</v>
+        <v>76.27543161000006</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -5344,16 +5353,16 @@
         <v>0.08</v>
       </c>
       <c r="C181">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D181">
-        <v>910.37495864</v>
+        <v>911.8211575</v>
       </c>
       <c r="E181">
-        <v>784.08606357</v>
+        <v>845.13725104</v>
       </c>
       <c r="F181">
-        <v>126.2888950700001</v>
+        <v>66.68390646</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5364,16 +5373,16 @@
         <v>0.08</v>
       </c>
       <c r="C182">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D182">
-        <v>908.06664447</v>
+        <v>909.8806273</v>
       </c>
       <c r="E182">
-        <v>786.7761219499999</v>
+        <v>849.89205236</v>
       </c>
       <c r="F182">
-        <v>121.2905225200001</v>
+        <v>59.98857494000003</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -5384,16 +5393,16 @@
         <v>0.08</v>
       </c>
       <c r="C183">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D183">
-        <v>905.0399585</v>
+        <v>907.2046422</v>
       </c>
       <c r="E183">
-        <v>786.77612263</v>
+        <v>851.74359567</v>
       </c>
       <c r="F183">
-        <v>118.26383587</v>
+        <v>55.46104652999998</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5404,16 +5413,16 @@
         <v>0.08</v>
       </c>
       <c r="C184">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D184">
-        <v>901.29944557</v>
+        <v>903.83541781</v>
       </c>
       <c r="E184">
-        <v>786.77612263</v>
+        <v>851.20057237</v>
       </c>
       <c r="F184">
-        <v>114.52332294</v>
+        <v>52.63484543999994</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -5424,16 +5433,16 @@
         <v>0.08</v>
       </c>
       <c r="C185">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D185">
-        <v>896.85392123</v>
+        <v>899.8019705</v>
       </c>
       <c r="E185">
-        <v>794.41261489</v>
+        <v>848.6078111</v>
       </c>
       <c r="F185">
-        <v>102.44130634</v>
+        <v>51.19415939999999</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5444,16 +5453,16 @@
         <v>0.08</v>
       </c>
       <c r="C186">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D186">
-        <v>891.71726145</v>
+        <v>895.12958478</v>
       </c>
       <c r="E186">
-        <v>805.78911938</v>
+        <v>844.2107038</v>
       </c>
       <c r="F186">
-        <v>85.92814207000004</v>
+        <v>50.91888097999993</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -5464,16 +5473,16 @@
         <v>0.08</v>
       </c>
       <c r="C187">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D187">
-        <v>885.90797241</v>
+        <v>889.84448532</v>
       </c>
       <c r="E187">
-        <v>812.63472285</v>
+        <v>843.7754462</v>
       </c>
       <c r="F187">
-        <v>73.27324955999995</v>
+        <v>46.06903911999996</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -5481,19 +5490,19 @@
         <v>192</v>
       </c>
       <c r="B188">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D188">
-        <v>910.72778464</v>
+        <v>883.97596422</v>
       </c>
       <c r="E188">
-        <v>820.74106227</v>
+        <v>843.48960234</v>
       </c>
       <c r="F188">
-        <v>89.98672236999994</v>
+        <v>40.48636188</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -5504,16 +5513,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C189">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D189">
-        <v>911.53561544</v>
+        <v>910.7313172200001</v>
       </c>
       <c r="E189">
-        <v>787.28979162</v>
+        <v>820.72647389</v>
       </c>
       <c r="F189">
-        <v>124.2458238200001</v>
+        <v>90.00484333000009</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -5524,16 +5533,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C190">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D190">
-        <v>911.48286962</v>
+        <v>911.76158169</v>
       </c>
       <c r="E190">
-        <v>780.86386547</v>
+        <v>820.4864978000001</v>
       </c>
       <c r="F190">
-        <v>130.61900415</v>
+        <v>91.27508388999991</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -5544,16 +5553,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C191">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D191">
-        <v>910.64969507</v>
+        <v>911.5864001</v>
       </c>
       <c r="E191">
-        <v>778.4033752</v>
+        <v>834.33001437</v>
       </c>
       <c r="F191">
-        <v>132.24631987</v>
+        <v>77.25638573000003</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -5564,16 +5573,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C192">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D192">
-        <v>909.06508264</v>
+        <v>910.45268829</v>
       </c>
       <c r="E192">
-        <v>783.68881042</v>
+        <v>843.04263485</v>
       </c>
       <c r="F192">
-        <v>125.37627222</v>
+        <v>67.41005343999996</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -5584,16 +5593,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C193">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D193">
-        <v>903.67024008</v>
+        <v>908.4941926499999</v>
       </c>
       <c r="E193">
-        <v>786.77612263</v>
+        <v>848.02176707</v>
       </c>
       <c r="F193">
-        <v>116.89411745</v>
+        <v>60.47242557999994</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -5604,16 +5613,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C194">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D194">
-        <v>899.86928711</v>
+        <v>905.7836403699999</v>
       </c>
       <c r="E194">
-        <v>786.77612263</v>
+        <v>850.07767559</v>
       </c>
       <c r="F194">
-        <v>113.0931644799999</v>
+        <v>55.70596477999993</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -5624,16 +5633,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C195">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D195">
-        <v>895.34533671</v>
+        <v>902.36441548</v>
       </c>
       <c r="E195">
-        <v>790.88165989</v>
+        <v>849.72416386</v>
       </c>
       <c r="F195">
-        <v>104.4636768199999</v>
+        <v>52.64025162000007</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -5644,16 +5653,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C196">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D196">
-        <v>890.11447363</v>
+        <v>898.26780559</v>
       </c>
       <c r="E196">
-        <v>803.5901477899999</v>
+        <v>847.30922421</v>
       </c>
       <c r="F196">
-        <v>86.52432584000007</v>
+        <v>50.95858137999994</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -5664,16 +5673,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C197">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D197">
-        <v>884.1974247000001</v>
+        <v>893.52196794</v>
       </c>
       <c r="E197">
-        <v>811.61986996</v>
+        <v>843.0801059299999</v>
       </c>
       <c r="F197">
-        <v>72.5775547400001</v>
+        <v>50.44186201000002</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -5681,19 +5690,19 @@
         <v>202</v>
       </c>
       <c r="B198">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D198">
-        <v>909.33233255</v>
+        <v>888.15631913</v>
       </c>
       <c r="E198">
-        <v>820.74106227</v>
+        <v>843.68156249</v>
       </c>
       <c r="F198">
-        <v>88.59127028</v>
+        <v>44.47475664000001</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -5701,19 +5710,19 @@
         <v>203</v>
       </c>
       <c r="B199">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C199">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D199">
-        <v>910.16662911</v>
+        <v>882.20353701</v>
       </c>
       <c r="E199">
-        <v>787.18636435</v>
+        <v>843.56543391</v>
       </c>
       <c r="F199">
-        <v>122.9802647600001</v>
+        <v>38.63810309999997</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -5724,16 +5733,16 @@
         <v>0.09</v>
       </c>
       <c r="C200">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D200">
-        <v>910.1426675599999</v>
+        <v>909.33587701</v>
       </c>
       <c r="E200">
-        <v>780.97003065</v>
+        <v>820.72630548</v>
       </c>
       <c r="F200">
-        <v>129.1726369099999</v>
+        <v>88.60957153000004</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -5744,16 +5753,16 @@
         <v>0.09</v>
       </c>
       <c r="C201">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D201">
-        <v>909.32608714</v>
+        <v>910.37559608</v>
       </c>
       <c r="E201">
-        <v>778.4033752</v>
+        <v>818.12133667</v>
       </c>
       <c r="F201">
-        <v>130.92271194</v>
+        <v>92.25425941000003</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -5764,16 +5773,16 @@
         <v>0.09</v>
       </c>
       <c r="C202">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D202">
-        <v>907.73900284</v>
+        <v>910.20694945</v>
       </c>
       <c r="E202">
-        <v>783.25093028</v>
+        <v>832.19724704</v>
       </c>
       <c r="F202">
-        <v>124.48807256</v>
+        <v>78.00970241000005</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -5784,16 +5793,16 @@
         <v>0.09</v>
       </c>
       <c r="C203">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D203">
-        <v>905.38739621</v>
+        <v>909.06766727</v>
       </c>
       <c r="E203">
-        <v>786.62268392</v>
+        <v>841.12089629</v>
       </c>
       <c r="F203">
-        <v>118.76471229</v>
+        <v>67.94677098</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -5804,16 +5813,16 @@
         <v>0.09</v>
       </c>
       <c r="C204">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D204">
-        <v>902.27484729</v>
+        <v>907.08771724</v>
       </c>
       <c r="E204">
-        <v>786.77612263</v>
+        <v>846.29349139</v>
       </c>
       <c r="F204">
-        <v>115.49872466</v>
+        <v>60.79422584999998</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -5824,16 +5833,16 @@
         <v>0.09</v>
       </c>
       <c r="C205">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D205">
-        <v>898.40858099</v>
+        <v>904.33930333</v>
       </c>
       <c r="E205">
-        <v>786.77612263</v>
+        <v>848.52926249</v>
       </c>
       <c r="F205">
-        <v>111.63245836</v>
+        <v>55.81004084000006</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -5844,16 +5853,16 @@
         <v>0.09</v>
       </c>
       <c r="C206">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D206">
-        <v>893.80142025</v>
+        <v>900.86718624</v>
       </c>
       <c r="E206">
-        <v>786.92455875</v>
+        <v>848.34481379</v>
       </c>
       <c r="F206">
-        <v>106.8768615</v>
+        <v>52.52237245000003</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -5864,16 +5873,16 @@
         <v>0.09</v>
       </c>
       <c r="C207">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D207">
-        <v>888.47173352</v>
+        <v>896.70510022</v>
       </c>
       <c r="E207">
-        <v>801.02557431</v>
+        <v>846.09001349</v>
       </c>
       <c r="F207">
-        <v>87.44615921000002</v>
+        <v>50.61508672999992</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -5884,16 +5893,16 @@
         <v>0.09</v>
       </c>
       <c r="C208">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D208">
-        <v>882.4425177099999</v>
+        <v>891.8842316</v>
       </c>
       <c r="E208">
-        <v>810.35093997</v>
+        <v>842.4214174799999</v>
       </c>
       <c r="F208">
-        <v>72.09157773999993</v>
+        <v>49.46281412000008</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -5901,19 +5910,19 @@
         <v>213</v>
       </c>
       <c r="B209">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D209">
-        <v>907.92845025</v>
+        <v>886.43734935</v>
       </c>
       <c r="E209">
-        <v>820.74106227</v>
+        <v>843.52870669</v>
       </c>
       <c r="F209">
-        <v>87.18738797999993</v>
+        <v>42.90864265999994</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -5921,19 +5930,19 @@
         <v>214</v>
       </c>
       <c r="B210">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="C210">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D210">
-        <v>908.78983533</v>
+        <v>880.40068514</v>
       </c>
       <c r="E210">
-        <v>787.18636435</v>
+        <v>843.71873436</v>
       </c>
       <c r="F210">
-        <v>121.60347098</v>
+        <v>36.68195077999997</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -5944,16 +5953,16 @@
         <v>0.095</v>
       </c>
       <c r="C211">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D211">
-        <v>908.79286113</v>
+        <v>907.93200346</v>
       </c>
       <c r="E211">
-        <v>781.07832134</v>
+        <v>820.72613288</v>
       </c>
       <c r="F211">
-        <v>127.71453979</v>
+        <v>87.20587058000001</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -5964,16 +5973,16 @@
         <v>0.095</v>
       </c>
       <c r="C212">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D212">
-        <v>907.98956016</v>
+        <v>908.97897697</v>
       </c>
       <c r="E212">
-        <v>778.4033752</v>
+        <v>816.00530307</v>
       </c>
       <c r="F212">
-        <v>129.58618496</v>
+        <v>92.97367389999999</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -5984,16 +5993,16 @@
         <v>0.095</v>
       </c>
       <c r="C213">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D213">
-        <v>906.39579065</v>
+        <v>908.81378995</v>
       </c>
       <c r="E213">
-        <v>782.76877159</v>
+        <v>830.25803267</v>
       </c>
       <c r="F213">
-        <v>123.62701906</v>
+        <v>78.55575727999997</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -6004,16 +6013,16 @@
         <v>0.095</v>
       </c>
       <c r="C214">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D214">
-        <v>904.01552997</v>
+        <v>907.66547412</v>
       </c>
       <c r="E214">
-        <v>786.49580924</v>
+        <v>839.35508496</v>
       </c>
       <c r="F214">
-        <v>117.51972073</v>
+        <v>68.31038916</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -6024,16 +6033,16 @@
         <v>0.095</v>
       </c>
       <c r="C215">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D215">
-        <v>900.85273047</v>
+        <v>905.66057396</v>
       </c>
       <c r="E215">
-        <v>786.77612263</v>
+        <v>844.6933146</v>
       </c>
       <c r="F215">
-        <v>114.07660784</v>
+        <v>60.96725935999996</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -6044,16 +6053,16 @@
         <v>0.095</v>
       </c>
       <c r="C216">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D216">
-        <v>896.91623147</v>
+        <v>902.8710394</v>
       </c>
       <c r="E216">
-        <v>786.77612263</v>
+        <v>847.08692053</v>
       </c>
       <c r="F216">
-        <v>110.1401088399999</v>
+        <v>55.78411886999993</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -6064,16 +6073,16 @@
         <v>0.095</v>
       </c>
       <c r="C217">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D217">
-        <v>892.22103987</v>
+        <v>899.34322407</v>
       </c>
       <c r="E217">
-        <v>786.77612263</v>
+        <v>847.05318247</v>
       </c>
       <c r="F217">
-        <v>105.44491724</v>
+        <v>52.2900416</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -6084,16 +6093,16 @@
         <v>0.095</v>
       </c>
       <c r="C218">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D218">
-        <v>886.78788022</v>
+        <v>895.11348816</v>
       </c>
       <c r="E218">
-        <v>798.05297304</v>
+        <v>844.94266166</v>
       </c>
       <c r="F218">
-        <v>88.73490718000005</v>
+        <v>50.17082649999998</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -6104,16 +6113,16 @@
         <v>0.095</v>
       </c>
       <c r="C219">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D219">
-        <v>880.64206229</v>
+        <v>890.21621735</v>
       </c>
       <c r="E219">
-        <v>808.78991694</v>
+        <v>842.05757465</v>
       </c>
       <c r="F219">
-        <v>71.85214535</v>
+        <v>48.15864269999997</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -6121,19 +6130,19 @@
         <v>224</v>
       </c>
       <c r="B220">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="C220">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D220">
-        <v>906.51575801</v>
+        <v>884.68770334</v>
       </c>
       <c r="E220">
-        <v>820.74106227</v>
+        <v>843.31834323</v>
       </c>
       <c r="F220">
-        <v>85.77469573999997</v>
+        <v>41.36936011</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -6141,19 +6150,19 @@
         <v>225</v>
       </c>
       <c r="B221">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="C221">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D221">
-        <v>907.40464593</v>
+        <v>878.56791863</v>
       </c>
       <c r="E221">
-        <v>787.18636435</v>
+        <v>843.79810204</v>
       </c>
       <c r="F221">
-        <v>120.2182815800001</v>
+        <v>34.76981659</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -6164,16 +6173,16 @@
         <v>0.1</v>
       </c>
       <c r="C222">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D222">
-        <v>907.43270837</v>
+        <v>906.51931656</v>
       </c>
       <c r="E222">
-        <v>781.18879581</v>
+        <v>820.7259567</v>
       </c>
       <c r="F222">
-        <v>126.24391256</v>
+        <v>85.79335986000001</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -6184,16 +6193,16 @@
         <v>0.1</v>
       </c>
       <c r="C223">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D223">
-        <v>906.63925834</v>
+        <v>907.5712227400001</v>
       </c>
       <c r="E223">
-        <v>778.4033752</v>
+        <v>815.26661517</v>
       </c>
       <c r="F223">
-        <v>128.2358831399999</v>
+        <v>92.30460757000003</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -6204,16 +6213,16 @@
         <v>0.1</v>
       </c>
       <c r="C224">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D224">
-        <v>905.0345035300001</v>
+        <v>907.40633745</v>
       </c>
       <c r="E224">
-        <v>782.23835305</v>
+        <v>828.49357472</v>
       </c>
       <c r="F224">
-        <v>122.7961504800001</v>
+        <v>78.91276273000005</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -6224,16 +6233,16 @@
         <v>0.1</v>
       </c>
       <c r="C225">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D225">
-        <v>902.62082671</v>
+        <v>906.24548194</v>
       </c>
       <c r="E225">
-        <v>786.34779027</v>
+        <v>837.73008923</v>
       </c>
       <c r="F225">
-        <v>116.2730364399999</v>
+        <v>68.51539271000001</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -6244,16 +6253,16 @@
         <v>0.1</v>
       </c>
       <c r="C226">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D226">
-        <v>899.40282447</v>
+        <v>904.2121356500001</v>
       </c>
       <c r="E226">
-        <v>786.77612263</v>
+        <v>843.20888926</v>
       </c>
       <c r="F226">
-        <v>112.62670184</v>
+        <v>61.00324639000007</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -6264,16 +6273,16 @@
         <v>0.1</v>
       </c>
       <c r="C227">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D227">
-        <v>895.39112979</v>
+        <v>901.37826996</v>
       </c>
       <c r="E227">
-        <v>786.77612263</v>
+        <v>845.74052384</v>
       </c>
       <c r="F227">
-        <v>108.61500716</v>
+        <v>55.63774611999997</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -6284,16 +6293,16 @@
         <v>0.1</v>
       </c>
       <c r="C228">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D228">
-        <v>890.60304702</v>
+        <v>897.7920456099999</v>
       </c>
       <c r="E228">
-        <v>786.77612263</v>
+        <v>845.84101316</v>
       </c>
       <c r="F228">
-        <v>103.8269243899999</v>
+        <v>51.95103244999996</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -6304,16 +6313,16 @@
         <v>0.1</v>
       </c>
       <c r="C229">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D229">
-        <v>885.06173182</v>
+        <v>893.49264558</v>
       </c>
       <c r="E229">
-        <v>794.62914906</v>
+        <v>843.8605258699999</v>
       </c>
       <c r="F229">
-        <v>90.43258275999995</v>
+        <v>49.6321197100001</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -6324,16 +6333,16 @@
         <v>0.1</v>
       </c>
       <c r="C230">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D230">
-        <v>878.794852</v>
+        <v>888.5178340799999</v>
       </c>
       <c r="E230">
-        <v>806.89342173</v>
+        <v>841.6600169</v>
       </c>
       <c r="F230">
-        <v>71.90143026999999</v>
+        <v>46.85781717999998</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -6341,19 +6350,19 @@
         <v>235</v>
       </c>
       <c r="B231">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D231">
-        <v>905.0938635</v>
+        <v>882.90761203</v>
       </c>
       <c r="E231">
-        <v>820.74106227</v>
+        <v>843.05264044</v>
       </c>
       <c r="F231">
-        <v>84.35280122999995</v>
+        <v>39.85497158999999</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -6361,19 +6370,19 @@
         <v>236</v>
       </c>
       <c r="B232">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="C232">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D232">
-        <v>906.01045967</v>
+        <v>876.70589622</v>
       </c>
       <c r="E232">
-        <v>787.18636435</v>
+        <v>843.80223405</v>
       </c>
       <c r="F232">
-        <v>118.8240953200001</v>
+        <v>32.90366216999996</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -6384,16 +6393,16 @@
         <v>0.105</v>
       </c>
       <c r="C233">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D233">
-        <v>906.0614556199999</v>
+        <v>905.09742369</v>
       </c>
       <c r="E233">
-        <v>781.3015140799999</v>
+        <v>820.72577582</v>
       </c>
       <c r="F233">
-        <v>124.75994154</v>
+        <v>84.37164787000006</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -6404,16 +6413,16 @@
         <v>0.105</v>
       </c>
       <c r="C234">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D234">
-        <v>905.27431223</v>
+        <v>906.15181937</v>
       </c>
       <c r="E234">
-        <v>778.4033752</v>
+        <v>815.22553211</v>
       </c>
       <c r="F234">
-        <v>126.8709370299999</v>
+        <v>90.92628725999998</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -6424,16 +6433,16 @@
         <v>0.105</v>
       </c>
       <c r="C235">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D235">
-        <v>903.6541846699999</v>
+        <v>905.98399761</v>
       </c>
       <c r="E235">
-        <v>781.65534646</v>
+        <v>826.8869752000001</v>
       </c>
       <c r="F235">
-        <v>121.9988382099999</v>
+        <v>79.09702240999991</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -6444,16 +6453,16 @@
         <v>0.105</v>
       </c>
       <c r="C236">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D236">
-        <v>901.2022610400001</v>
+        <v>904.80705828</v>
       </c>
       <c r="E236">
-        <v>786.17657521</v>
+        <v>836.23239934</v>
       </c>
       <c r="F236">
-        <v>115.02568583</v>
+        <v>68.57465893999995</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -6464,16 +6473,16 @@
         <v>0.105</v>
       </c>
       <c r="C237">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D237">
-        <v>897.92404858</v>
+        <v>902.74177575</v>
       </c>
       <c r="E237">
-        <v>786.77612263</v>
+        <v>841.8292162499999</v>
       </c>
       <c r="F237">
-        <v>111.1479259499999</v>
+        <v>60.91255950000004</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -6484,16 +6493,16 @@
         <v>0.105</v>
       </c>
       <c r="C238">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D238">
-        <v>893.83214868</v>
+        <v>899.86042172</v>
       </c>
       <c r="E238">
-        <v>786.77612263</v>
+        <v>844.48107758</v>
       </c>
       <c r="F238">
-        <v>107.05602605</v>
+        <v>55.37934413999994</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -6504,16 +6513,16 @@
         <v>0.105</v>
       </c>
       <c r="C239">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D239">
-        <v>888.94627676</v>
+        <v>896.21319465</v>
       </c>
       <c r="E239">
-        <v>786.77612263</v>
+        <v>844.70098232</v>
       </c>
       <c r="F239">
-        <v>102.17015413</v>
+        <v>51.51221233000001</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -6524,16 +6533,16 @@
         <v>0.105</v>
       </c>
       <c r="C240">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D240">
-        <v>883.29209048</v>
+        <v>891.84229793</v>
       </c>
       <c r="E240">
-        <v>790.71308494</v>
+        <v>842.83771941</v>
       </c>
       <c r="F240">
-        <v>92.57900553999991</v>
+        <v>49.00457852</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -6544,16 +6553,16 @@
         <v>0.105</v>
       </c>
       <c r="C241">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D241">
-        <v>876.89966286</v>
+        <v>886.7890697399999</v>
       </c>
       <c r="E241">
-        <v>804.61243394</v>
+        <v>841.23221455</v>
       </c>
       <c r="F241">
-        <v>72.28722892000008</v>
+        <v>45.55685518999996</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -6561,19 +6570,19 @@
         <v>246</v>
       </c>
       <c r="B242">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="C242">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D242">
-        <v>903.66236139</v>
+        <v>881.09742417</v>
       </c>
       <c r="E242">
-        <v>820.74106227</v>
+        <v>842.7344518</v>
       </c>
       <c r="F242">
-        <v>82.92129911999996</v>
+        <v>38.36297236999997</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -6581,19 +6590,19 @@
         <v>247</v>
       </c>
       <c r="B243">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="C243">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D243">
-        <v>904.60666268</v>
+        <v>874.81544453</v>
       </c>
       <c r="E243">
-        <v>787.18636435</v>
+        <v>843.73073041</v>
       </c>
       <c r="F243">
-        <v>117.42029833</v>
+        <v>31.08471412000006</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -6604,16 +6613,16 @@
         <v>0.11</v>
       </c>
       <c r="C244">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D244">
-        <v>904.67833288</v>
+        <v>903.66591924</v>
       </c>
       <c r="E244">
-        <v>781.41653746</v>
+        <v>820.72559105</v>
       </c>
       <c r="F244">
-        <v>123.26179542</v>
+        <v>82.94032818999995</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -6624,16 +6633,16 @@
         <v>0.11</v>
       </c>
       <c r="C245">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D245">
-        <v>903.89383848</v>
+        <v>904.7202406500001</v>
       </c>
       <c r="E245">
-        <v>778.4033752</v>
+        <v>815.18400569</v>
       </c>
       <c r="F245">
-        <v>125.49046328</v>
+        <v>89.53623496</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -6644,16 +6653,16 @@
         <v>0.11</v>
       </c>
       <c r="C246">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D246">
-        <v>902.25386313</v>
+        <v>904.54616633</v>
       </c>
       <c r="E246">
-        <v>781.01506549</v>
+        <v>825.42301442</v>
       </c>
       <c r="F246">
-        <v>121.23879764</v>
+        <v>79.12315191000005</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -6664,16 +6673,16 @@
         <v>0.11</v>
       </c>
       <c r="C247">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D247">
-        <v>899.75879219</v>
+        <v>903.34956631</v>
       </c>
       <c r="E247">
-        <v>785.97989107</v>
+        <v>834.84990656</v>
       </c>
       <c r="F247">
-        <v>113.77890112</v>
+        <v>68.49965974999998</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -6684,16 +6693,16 @@
         <v>0.11</v>
       </c>
       <c r="C248">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D248">
-        <v>896.41530584</v>
+        <v>901.24887338</v>
       </c>
       <c r="E248">
-        <v>786.77612263</v>
+        <v>840.5444742</v>
       </c>
       <c r="F248">
-        <v>109.6391832099999</v>
+        <v>60.70439918</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -6704,16 +6713,16 @@
         <v>0.11</v>
       </c>
       <c r="C249">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D249">
-        <v>892.2381448899999</v>
+        <v>898.31694161</v>
       </c>
       <c r="E249">
-        <v>786.77612263</v>
+        <v>843.30056812</v>
       </c>
       <c r="F249">
-        <v>105.4620222599999</v>
+        <v>55.01637348999998</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -6724,16 +6733,16 @@
         <v>0.11</v>
       </c>
       <c r="C250">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D250">
-        <v>887.24954597</v>
+        <v>894.60624704</v>
       </c>
       <c r="E250">
-        <v>786.77612263</v>
+        <v>843.62657595</v>
       </c>
       <c r="F250">
-        <v>100.47342334</v>
+        <v>50.97967109000001</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -6744,16 +6753,16 @@
         <v>0.11</v>
       </c>
       <c r="C251">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D251">
-        <v>881.47774186</v>
+        <v>890.16222594</v>
       </c>
       <c r="E251">
-        <v>786.77612263</v>
+        <v>841.86901144</v>
       </c>
       <c r="F251">
-        <v>94.70161923000001</v>
+        <v>48.29321449999998</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -6764,16 +6773,16 @@
         <v>0.11</v>
       </c>
       <c r="C252">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D252">
-        <v>874.95525303</v>
+        <v>885.0300019699999</v>
       </c>
       <c r="E252">
-        <v>801.8924393999999</v>
+        <v>840.77779369</v>
       </c>
       <c r="F252">
-        <v>73.06281363000005</v>
+        <v>44.25220827999999</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -6781,19 +6790,19 @@
         <v>257</v>
       </c>
       <c r="B253">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="C253">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D253">
-        <v>902.2208331099999</v>
+        <v>879.25762227</v>
       </c>
       <c r="E253">
-        <v>820.74106227</v>
+        <v>842.36726743</v>
       </c>
       <c r="F253">
-        <v>81.4797708399999</v>
+        <v>36.89035483999999</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -6801,19 +6810,19 @@
         <v>258</v>
       </c>
       <c r="B254">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="C254">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D254">
-        <v>903.1926265</v>
+        <v>872.89758008</v>
       </c>
       <c r="E254">
-        <v>787.18636435</v>
+        <v>843.58420203</v>
       </c>
       <c r="F254">
-        <v>116.00626215</v>
+        <v>29.31337804999998</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -6824,16 +6833,16 @@
         <v>0.115</v>
       </c>
       <c r="C255">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D255">
-        <v>903.28255942</v>
+        <v>902.22438436</v>
       </c>
       <c r="E255">
-        <v>781.53392946</v>
+        <v>820.72540125</v>
       </c>
       <c r="F255">
-        <v>121.74862996</v>
+        <v>81.49898311000004</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -6844,16 +6853,16 @@
         <v>0.115</v>
       </c>
       <c r="C256">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D256">
-        <v>902.49693949</v>
+        <v>903.27594809</v>
       </c>
       <c r="E256">
-        <v>778.4033752</v>
+        <v>815.14203735</v>
       </c>
       <c r="F256">
-        <v>124.09356429</v>
+        <v>88.13391074000003</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -6864,16 +6873,16 @@
         <v>0.115</v>
       </c>
       <c r="C257">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D257">
-        <v>900.8325512599999</v>
+        <v>903.0922301000001</v>
       </c>
       <c r="E257">
-        <v>780.31246408</v>
+        <v>824.08796043</v>
       </c>
       <c r="F257">
-        <v>120.5200871799999</v>
+        <v>79.0042696700001</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -6884,16 +6893,16 @@
         <v>0.115</v>
       </c>
       <c r="C258">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D258">
-        <v>898.28936387</v>
+        <v>901.87236219</v>
       </c>
       <c r="E258">
-        <v>785.75521725</v>
+        <v>833.5717329</v>
       </c>
       <c r="F258">
-        <v>112.53414662</v>
+        <v>68.30062928999996</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -6904,16 +6913,16 @@
         <v>0.115</v>
       </c>
       <c r="C259">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D259">
-        <v>894.87548288</v>
+        <v>899.73280678</v>
       </c>
       <c r="E259">
-        <v>786.77612263</v>
+        <v>839.34586877</v>
       </c>
       <c r="F259">
-        <v>108.09936025</v>
+        <v>60.38693800999999</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -6924,16 +6933,16 @@
         <v>0.115</v>
       </c>
       <c r="C260">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D260">
-        <v>890.60795682</v>
+        <v>896.74729215</v>
       </c>
       <c r="E260">
-        <v>786.77612263</v>
+        <v>842.19183752</v>
       </c>
       <c r="F260">
-        <v>103.83183419</v>
+        <v>54.55545462999999</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -6944,16 +6953,16 @@
         <v>0.115</v>
       </c>
       <c r="C261">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D261">
-        <v>885.5116546100001</v>
+        <v>892.97081568</v>
       </c>
       <c r="E261">
-        <v>786.77612263</v>
+        <v>842.61198597</v>
       </c>
       <c r="F261">
-        <v>98.73553198000002</v>
+        <v>50.35882971000001</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -6964,16 +6973,16 @@
         <v>0.115</v>
       </c>
       <c r="C262">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D262">
-        <v>879.61745216</v>
+        <v>888.4522769599999</v>
       </c>
       <c r="E262">
-        <v>786.77612263</v>
+        <v>840.94974403</v>
       </c>
       <c r="F262">
-        <v>92.84132952999994</v>
+        <v>47.50253292999992</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -6984,16 +6993,16 @@
         <v>0.115</v>
       </c>
       <c r="C263">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D263">
-        <v>872.96036256</v>
+        <v>883.24081122</v>
       </c>
       <c r="E263">
-        <v>798.67437482</v>
+        <v>840.3004512</v>
       </c>
       <c r="F263">
-        <v>74.28598774</v>
+        <v>42.94036001999996</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -7001,19 +7010,19 @@
         <v>268</v>
       </c>
       <c r="B264">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="C264">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D264">
-        <v>900.76884653</v>
+        <v>877.3888414</v>
       </c>
       <c r="E264">
-        <v>820.74106227</v>
+        <v>841.95513525</v>
       </c>
       <c r="F264">
-        <v>80.02778425999998</v>
+        <v>35.43370615000003</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -7021,19 +7030,19 @@
         <v>269</v>
       </c>
       <c r="B265">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="C265">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D265">
-        <v>901.76771064</v>
+        <v>870.9535339400001</v>
       </c>
       <c r="E265">
-        <v>787.18636435</v>
+        <v>843.36434767</v>
       </c>
       <c r="F265">
-        <v>114.5813462900001</v>
+        <v>27.58918627000003</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -7044,16 +7053,16 @@
         <v>0.12</v>
       </c>
       <c r="C266">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D266">
-        <v>901.87333902</v>
+        <v>900.77238661</v>
       </c>
       <c r="E266">
-        <v>781.6537548699999</v>
+        <v>820.725207</v>
       </c>
       <c r="F266">
-        <v>120.2195841500001</v>
+        <v>80.04717961000006</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -7064,16 +7073,16 @@
         <v>0.12</v>
       </c>
       <c r="C267">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D267">
-        <v>901.08270332</v>
+        <v>901.81839023</v>
       </c>
       <c r="E267">
-        <v>778.4033752</v>
+        <v>815.0996291599999</v>
       </c>
       <c r="F267">
-        <v>122.6793281199999</v>
+        <v>86.71876107000003</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -7084,16 +7093,16 @@
         <v>0.12</v>
       </c>
       <c r="C268">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D268">
-        <v>899.3892488</v>
+        <v>901.62156539</v>
       </c>
       <c r="E268">
-        <v>779.54214967</v>
+        <v>822.86940399</v>
       </c>
       <c r="F268">
-        <v>119.8470991300001</v>
+        <v>78.75216139999998</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -7104,16 +7113,16 @@
         <v>0.12</v>
       </c>
       <c r="C269">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D269">
-        <v>896.79290367</v>
+        <v>900.37480204</v>
       </c>
       <c r="E269">
-        <v>785.49975594</v>
+        <v>832.3880861</v>
       </c>
       <c r="F269">
-        <v>111.29314773</v>
+        <v>67.98671593999995</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -7124,16 +7133,16 @@
         <v>0.12</v>
       </c>
       <c r="C270">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D270">
-        <v>893.30344992</v>
+        <v>898.19296524</v>
       </c>
       <c r="E270">
-        <v>786.77612263</v>
+        <v>838.2255084</v>
       </c>
       <c r="F270">
-        <v>106.52732729</v>
+        <v>59.96745684000007</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -7144,16 +7153,16 @@
         <v>0.12</v>
       </c>
       <c r="C271">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D271">
-        <v>888.94040684</v>
+        <v>895.15095754</v>
       </c>
       <c r="E271">
-        <v>786.77612263</v>
+        <v>841.14847895</v>
       </c>
       <c r="F271">
-        <v>102.16428421</v>
+        <v>54.00247859000001</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -7164,16 +7173,16 @@
         <v>0.12</v>
       </c>
       <c r="C272">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D272">
-        <v>883.73138402</v>
+        <v>891.30655869</v>
       </c>
       <c r="E272">
-        <v>786.77612263</v>
+        <v>841.65202331</v>
       </c>
       <c r="F272">
-        <v>96.95526138999992</v>
+        <v>49.65453537999997</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -7184,16 +7193,16 @@
         <v>0.12</v>
       </c>
       <c r="C273">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D273">
-        <v>877.70996953</v>
+        <v>886.7123724</v>
       </c>
       <c r="E273">
-        <v>786.77612263</v>
+        <v>840.0757621400001</v>
       </c>
       <c r="F273">
-        <v>90.93384689999993</v>
+        <v>46.63661026</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -7204,16 +7213,16 @@
         <v>0.12</v>
       </c>
       <c r="C274">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D274">
-        <v>870.91371312</v>
+        <v>881.42179542</v>
       </c>
       <c r="E274">
-        <v>794.89698813</v>
+        <v>839.80387473</v>
       </c>
       <c r="F274">
-        <v>76.01672499000006</v>
+        <v>41.61792069000001</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -7221,19 +7230,19 @@
         <v>279</v>
       </c>
       <c r="B275">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="C275">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D275">
-        <v>899.30595552</v>
+        <v>875.4918896200001</v>
       </c>
       <c r="E275">
-        <v>820.74106227</v>
+        <v>841.50255598</v>
       </c>
       <c r="F275">
-        <v>78.56489324999995</v>
+        <v>33.98933364000004</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -7241,19 +7250,19 @@
         <v>280</v>
       </c>
       <c r="B276">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="C276">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D276">
-        <v>900.3312598799999</v>
+        <v>868.98477912</v>
       </c>
       <c r="E276">
-        <v>787.18636435</v>
+        <v>843.07398741</v>
       </c>
       <c r="F276">
-        <v>113.14489553</v>
+        <v>25.91079171000001</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -7264,16 +7273,16 @@
         <v>0.125</v>
       </c>
       <c r="C277">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D277">
-        <v>900.44986156</v>
+        <v>899.30947962</v>
       </c>
       <c r="E277">
-        <v>781.77608017</v>
+        <v>820.72500787</v>
       </c>
       <c r="F277">
-        <v>118.67378139</v>
+        <v>78.58447175000003</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -7284,16 +7293,16 @@
         <v>0.125</v>
       </c>
       <c r="C278">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D278">
-        <v>899.6502025999999</v>
+        <v>900.3470037</v>
       </c>
       <c r="E278">
-        <v>778.4033752</v>
+        <v>815.05678382</v>
       </c>
       <c r="F278">
-        <v>121.2468273999999</v>
+        <v>85.29021988</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -7304,16 +7313,16 @@
         <v>0.125</v>
       </c>
       <c r="C279">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D279">
-        <v>897.92293761</v>
+        <v>900.13354047</v>
       </c>
       <c r="E279">
-        <v>778.6984179</v>
+        <v>821.75611508</v>
       </c>
       <c r="F279">
-        <v>119.22451971</v>
+        <v>78.37742538999998</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -7324,16 +7333,16 @@
         <v>0.125</v>
       </c>
       <c r="C280">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D280">
-        <v>895.26832286</v>
+        <v>898.85623808</v>
       </c>
       <c r="E280">
-        <v>785.2103991</v>
+        <v>831.2901355400001</v>
       </c>
       <c r="F280">
-        <v>110.05792376</v>
+        <v>67.56610253999997</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -7344,16 +7353,16 @@
         <v>0.125</v>
       </c>
       <c r="C281">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D281">
-        <v>891.69805877</v>
+        <v>896.62874461</v>
       </c>
       <c r="E281">
-        <v>786.77612263</v>
+        <v>837.17629805</v>
       </c>
       <c r="F281">
-        <v>104.92193614</v>
+        <v>59.45244656</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -7364,16 +7373,16 @@
         <v>0.125</v>
       </c>
       <c r="C282">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D282">
-        <v>887.23429913</v>
+        <v>893.52744765</v>
       </c>
       <c r="E282">
-        <v>786.77612263</v>
+        <v>840.16474705</v>
       </c>
       <c r="F282">
-        <v>100.4581764999999</v>
+        <v>53.36270060000004</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -7384,16 +7393,16 @@
         <v>0.125</v>
       </c>
       <c r="C283">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D283">
-        <v>881.90749724</v>
+        <v>889.61318204</v>
       </c>
       <c r="E283">
-        <v>786.77612263</v>
+        <v>840.74204428</v>
       </c>
       <c r="F283">
-        <v>95.13137460999997</v>
+        <v>48.87113776000001</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -7404,16 +7413,16 @@
         <v>0.125</v>
       </c>
       <c r="C284">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D284">
-        <v>875.75402357</v>
+        <v>884.94251994</v>
       </c>
       <c r="E284">
-        <v>786.77612263</v>
+        <v>839.24335448</v>
       </c>
       <c r="F284">
-        <v>88.97790093999993</v>
+        <v>45.69916546000002</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -7424,16 +7433,16 @@
         <v>0.125</v>
       </c>
       <c r="C285">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D285">
-        <v>868.81400806</v>
+        <v>879.57338692</v>
       </c>
       <c r="E285">
-        <v>790.50149062</v>
+        <v>839.29166285</v>
       </c>
       <c r="F285">
-        <v>78.31251743999997</v>
+        <v>40.28172407</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -7441,19 +7450,19 @@
         <v>290</v>
       </c>
       <c r="B286">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="C286">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D286">
-        <v>897.83170009</v>
+        <v>873.56777195</v>
       </c>
       <c r="E286">
-        <v>820.74106227</v>
+        <v>841.01435723</v>
       </c>
       <c r="F286">
-        <v>77.09063781999998</v>
+        <v>32.55341471999998</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -7461,19 +7470,19 @@
         <v>291</v>
       </c>
       <c r="B287">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="C287">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D287">
-        <v>898.88260528</v>
+        <v>866.99306167</v>
       </c>
       <c r="E287">
-        <v>787.18636435</v>
+        <v>842.71704256</v>
       </c>
       <c r="F287">
-        <v>111.69624093</v>
+        <v>24.27601910999999</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -7484,16 +7493,16 @@
         <v>0.13</v>
       </c>
       <c r="C288">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D288">
-        <v>899.01130123</v>
+        <v>897.83520307</v>
       </c>
       <c r="E288">
-        <v>781.9009734</v>
+        <v>820.72480368</v>
       </c>
       <c r="F288">
-        <v>117.11032783</v>
+        <v>77.11039939</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -7504,16 +7513,16 @@
         <v>0.13</v>
       </c>
       <c r="C289">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D289">
-        <v>898.19849557</v>
+        <v>898.861211</v>
       </c>
       <c r="E289">
-        <v>778.4033752</v>
+        <v>815.01350533</v>
       </c>
       <c r="F289">
-        <v>119.7951203699999</v>
+        <v>83.84770566999998</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -7524,16 +7533,16 @@
         <v>0.13</v>
       </c>
       <c r="C290">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D290">
-        <v>896.43258694</v>
+        <v>898.62751428</v>
       </c>
       <c r="E290">
-        <v>778.4033752</v>
+        <v>820.73791815</v>
       </c>
       <c r="F290">
-        <v>118.0292117399999</v>
+        <v>77.88959612999997</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -7544,16 +7553,16 @@
         <v>0.13</v>
       </c>
       <c r="C291">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D291">
-        <v>893.71451601</v>
+        <v>897.31602128</v>
       </c>
       <c r="E291">
-        <v>784.88369205</v>
+        <v>830.26990559</v>
       </c>
       <c r="F291">
-        <v>108.83082396</v>
+        <v>67.04611568999997</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -7564,16 +7573,16 @@
         <v>0.13</v>
       </c>
       <c r="C292">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D292">
-        <v>890.05814496</v>
+        <v>895.03955229</v>
       </c>
       <c r="E292">
-        <v>786.77612263</v>
+        <v>836.19185082</v>
       </c>
       <c r="F292">
-        <v>103.28202233</v>
+        <v>58.84770146999995</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -7584,16 +7593,16 @@
         <v>0.13</v>
       </c>
       <c r="C293">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D293">
-        <v>885.4884187</v>
+        <v>891.87630337</v>
       </c>
       <c r="E293">
-        <v>786.77612263</v>
+        <v>839.23548155</v>
       </c>
       <c r="F293">
-        <v>98.71229606999998</v>
+        <v>52.64082181999993</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -7604,16 +7613,16 @@
         <v>0.13</v>
       </c>
       <c r="C294">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D294">
-        <v>880.0387385</v>
+        <v>887.8904530900001</v>
       </c>
       <c r="E294">
-        <v>786.77612263</v>
+        <v>839.8778882300001</v>
       </c>
       <c r="F294">
-        <v>93.26261586999999</v>
+        <v>48.01256486</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -7624,16 +7633,16 @@
         <v>0.13</v>
       </c>
       <c r="C295">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D295">
-        <v>873.74832465</v>
+        <v>883.14282645</v>
       </c>
       <c r="E295">
-        <v>786.77612263</v>
+        <v>838.44920304</v>
       </c>
       <c r="F295">
-        <v>86.97220201999994</v>
+        <v>44.69362340999999</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -7644,16 +7653,16 @@
         <v>0.13</v>
       </c>
       <c r="C296">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D296">
-        <v>866.6599303</v>
+        <v>877.69617208</v>
       </c>
       <c r="E296">
-        <v>786.77612263</v>
+        <v>838.76725931</v>
       </c>
       <c r="F296">
-        <v>79.88380767000001</v>
+        <v>38.92891277000001</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -7661,19 +7670,19 @@
         <v>301</v>
       </c>
       <c r="B297">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="C297">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D297">
-        <v>896.34560554</v>
+        <v>871.61771722</v>
       </c>
       <c r="E297">
-        <v>820.74106227</v>
+        <v>840.4955551199999</v>
       </c>
       <c r="F297">
-        <v>75.60454326999991</v>
+        <v>31.12216210000008</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -7681,19 +7690,19 @@
         <v>302</v>
       </c>
       <c r="B298">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="C298">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D298">
-        <v>897.42106087</v>
+        <v>864.9804343</v>
       </c>
       <c r="E298">
-        <v>787.18636435</v>
+        <v>842.29845557</v>
       </c>
       <c r="F298">
-        <v>110.2346965200001</v>
+        <v>22.68197872999997</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -7704,16 +7713,16 @@
         <v>0.135</v>
       </c>
       <c r="C299">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D299">
-        <v>897.55682114</v>
+        <v>896.34908201</v>
       </c>
       <c r="E299">
-        <v>782.0285041</v>
+        <v>820.72459422</v>
       </c>
       <c r="F299">
-        <v>115.52831704</v>
+        <v>75.62448778999999</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -7724,16 +7733,16 @@
         <v>0.135</v>
       </c>
       <c r="C300">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D300">
-        <v>896.7266247</v>
+        <v>897.36042593</v>
       </c>
       <c r="E300">
-        <v>778.4033752</v>
+        <v>814.96979816</v>
       </c>
       <c r="F300">
-        <v>118.3232495</v>
+        <v>82.39062777000004</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -7744,16 +7753,16 @@
         <v>0.135</v>
       </c>
       <c r="C301">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D301">
-        <v>894.9171454</v>
+        <v>897.10283792</v>
       </c>
       <c r="E301">
-        <v>778.4033752</v>
+        <v>819.8055831</v>
       </c>
       <c r="F301">
-        <v>116.5137702</v>
+        <v>77.29725481999992</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -7764,16 +7773,16 @@
         <v>0.135</v>
       </c>
       <c r="C302">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D302">
-        <v>892.13036129</v>
+        <v>895.7535027500001</v>
       </c>
       <c r="E302">
-        <v>784.5157934699999</v>
+        <v>829.32018354</v>
       </c>
       <c r="F302">
-        <v>107.61456782</v>
+        <v>66.43331921000004</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -7784,16 +7793,16 @@
         <v>0.135</v>
       </c>
       <c r="C303">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D303">
-        <v>888.38252589</v>
+        <v>893.42480982</v>
       </c>
       <c r="E303">
-        <v>786.77612263</v>
+        <v>835.2664059700001</v>
       </c>
       <c r="F303">
-        <v>101.60640326</v>
+        <v>58.1584038499999</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -7804,16 +7813,16 @@
         <v>0.135</v>
       </c>
       <c r="C304">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D304">
-        <v>883.7015326</v>
+        <v>890.19709943</v>
       </c>
       <c r="E304">
-        <v>786.77612263</v>
+        <v>838.3560434</v>
       </c>
       <c r="F304">
-        <v>96.92540996999992</v>
+        <v>51.84105603</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -7824,16 +7833,16 @@
         <v>0.135</v>
       </c>
       <c r="C305">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D305">
-        <v>878.12383273</v>
+        <v>886.13820661</v>
       </c>
       <c r="E305">
-        <v>786.77612263</v>
+        <v>839.0558237</v>
       </c>
       <c r="F305">
-        <v>91.34771009999997</v>
+        <v>47.08238290999998</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -7844,16 +7853,16 @@
         <v>0.135</v>
       </c>
       <c r="C306">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D306">
-        <v>871.69156378</v>
+        <v>881.31351384</v>
       </c>
       <c r="E306">
-        <v>786.77612263</v>
+        <v>837.69033985</v>
       </c>
       <c r="F306">
-        <v>84.91544114999999</v>
+        <v>43.62317399000005</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -7864,16 +7873,16 @@
         <v>0.135</v>
       </c>
       <c r="C307">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D307">
-        <v>864.450146</v>
+        <v>875.79091333</v>
       </c>
       <c r="E307">
-        <v>786.77612263</v>
+        <v>838.23390029</v>
       </c>
       <c r="F307">
-        <v>77.67402336999999</v>
+        <v>37.55701304000002</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -7881,19 +7890,19 @@
         <v>312</v>
       </c>
       <c r="B308">
-        <v>0.14</v>
+        <v>0.135</v>
       </c>
       <c r="C308">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D308">
-        <v>894.84718246</v>
+        <v>869.6432084100001</v>
       </c>
       <c r="E308">
-        <v>820.74106227</v>
+        <v>839.95121367</v>
       </c>
       <c r="F308">
-        <v>74.10612018999996</v>
+        <v>29.69199474000004</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -7901,19 +7910,19 @@
         <v>313</v>
       </c>
       <c r="B309">
-        <v>0.14</v>
+        <v>0.135</v>
       </c>
       <c r="C309">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D309">
-        <v>895.94593199</v>
+        <v>862.9492939199999</v>
       </c>
       <c r="E309">
-        <v>787.18636435</v>
+        <v>841.82405005</v>
       </c>
       <c r="F309">
-        <v>108.75956764</v>
+        <v>21.12524386999996</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -7924,16 +7933,16 @@
         <v>0.14</v>
       </c>
       <c r="C310">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D310">
-        <v>896.08556388</v>
+        <v>894.8506267400001</v>
       </c>
       <c r="E310">
-        <v>782.1587432</v>
+        <v>820.7243793</v>
       </c>
       <c r="F310">
-        <v>113.92682068</v>
+        <v>74.12624744000004</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -7944,16 +7953,16 @@
         <v>0.14</v>
       </c>
       <c r="C311">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D311">
-        <v>895.23361683</v>
+        <v>895.8440434</v>
       </c>
       <c r="E311">
-        <v>778.4033752</v>
+        <v>814.92566829</v>
       </c>
       <c r="F311">
-        <v>116.8302416299999</v>
+        <v>80.91837511000006</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -7964,16 +7973,16 @@
         <v>0.14</v>
       </c>
       <c r="C312">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D312">
-        <v>893.3755479500001</v>
+        <v>895.55885446</v>
       </c>
       <c r="E312">
-        <v>778.4033752</v>
+        <v>818.95073007</v>
       </c>
       <c r="F312">
-        <v>114.97217275</v>
+        <v>76.60812439000006</v>
       </c>
     </row>
     <row r="313" spans="1:6">
@@ -7984,16 +7993,16 @@
         <v>0.14</v>
       </c>
       <c r="C313">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D313">
-        <v>890.51471659</v>
+        <v>894.16803539</v>
       </c>
       <c r="E313">
-        <v>784.1024322</v>
+        <v>828.43444082</v>
       </c>
       <c r="F313">
-        <v>106.4122843900001</v>
+        <v>65.73359457000004</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -8004,16 +8013,16 @@
         <v>0.14</v>
       </c>
       <c r="C314">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D314">
-        <v>886.67000031</v>
+        <v>891.78395683</v>
       </c>
       <c r="E314">
-        <v>786.77612263</v>
+        <v>834.39476646</v>
       </c>
       <c r="F314">
-        <v>99.89387767999995</v>
+        <v>57.38919036999994</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -8024,16 +8033,16 @@
         <v>0.14</v>
       </c>
       <c r="C315">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D315">
-        <v>881.872389</v>
+        <v>888.4894560499999</v>
       </c>
       <c r="E315">
-        <v>786.77612263</v>
+        <v>837.52225839</v>
       </c>
       <c r="F315">
-        <v>95.09626636999997</v>
+        <v>50.9671976599999</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -8044,16 +8053,16 @@
         <v>0.14</v>
       </c>
       <c r="C316">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D316">
-        <v>876.16148551</v>
+        <v>884.35635704</v>
       </c>
       <c r="E316">
-        <v>786.77612263</v>
+        <v>838.27250273</v>
       </c>
       <c r="F316">
-        <v>89.38536288</v>
+        <v>46.08385430999999</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -8064,16 +8073,16 @@
         <v>0.14</v>
       </c>
       <c r="C317">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D317">
-        <v>869.58241249</v>
+        <v>879.45493468</v>
       </c>
       <c r="E317">
-        <v>786.77612263</v>
+        <v>836.96411002</v>
       </c>
       <c r="F317">
-        <v>82.80628985999999</v>
+        <v>42.49082465999993</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -8084,16 +8093,16 @@
         <v>0.14</v>
       </c>
       <c r="C318">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D318">
-        <v>862.18330041</v>
+        <v>873.8585749</v>
       </c>
       <c r="E318">
-        <v>786.77612263</v>
+        <v>837.69457031</v>
       </c>
       <c r="F318">
-        <v>75.40717777999998</v>
+        <v>36.16400458999999</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -8101,19 +8110,19 @@
         <v>323</v>
       </c>
       <c r="B319">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="C319">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D319">
-        <v>893.33592637</v>
+        <v>867.64601707</v>
       </c>
       <c r="E319">
-        <v>820.74106227</v>
+        <v>839.38630882</v>
       </c>
       <c r="F319">
-        <v>72.5948641</v>
+        <v>28.25970825000002</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -8121,19 +8130,19 @@
         <v>324</v>
       </c>
       <c r="B320">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="C320">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D320">
-        <v>894.45650039</v>
+        <v>860.90242191</v>
       </c>
       <c r="E320">
-        <v>787.18636435</v>
+        <v>841.30033789</v>
       </c>
       <c r="F320">
-        <v>107.27013604</v>
+        <v>19.60208402000001</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -8144,16 +8153,16 @@
         <v>0.145</v>
       </c>
       <c r="C321">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D321">
-        <v>894.59665995</v>
+        <v>893.33933251</v>
       </c>
       <c r="E321">
-        <v>782.29176291</v>
+        <v>820.72415869</v>
       </c>
       <c r="F321">
-        <v>112.30489704</v>
+        <v>72.61517382</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -8164,16 +8173,16 @@
         <v>0.145</v>
       </c>
       <c r="C322">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D322">
-        <v>893.7184819399999</v>
+        <v>894.31145143</v>
       </c>
       <c r="E322">
-        <v>778.4033752</v>
+        <v>814.88112258</v>
       </c>
       <c r="F322">
-        <v>115.3151067399999</v>
+        <v>79.43032885000002</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -8184,16 +8193,16 @@
         <v>0.145</v>
       </c>
       <c r="C323">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D323">
-        <v>891.80671227</v>
+        <v>893.99489996</v>
       </c>
       <c r="E323">
-        <v>778.4033752</v>
+        <v>818.16574558</v>
       </c>
       <c r="F323">
-        <v>113.40333707</v>
+        <v>75.82915437999998</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -8204,16 +8213,16 @@
         <v>0.145</v>
       </c>
       <c r="C324">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D324">
-        <v>888.86642608</v>
+        <v>892.55897519</v>
       </c>
       <c r="E324">
-        <v>783.63886141</v>
+        <v>827.60676186</v>
       </c>
       <c r="F324">
-        <v>105.22756467</v>
+        <v>64.95221332999995</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -8224,16 +8233,16 @@
         <v>0.145</v>
       </c>
       <c r="C325">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D325">
-        <v>884.91934825</v>
+        <v>890.11645249</v>
       </c>
       <c r="E325">
-        <v>786.77612263</v>
+        <v>833.5722388299999</v>
       </c>
       <c r="F325">
-        <v>98.14322561999995</v>
+        <v>56.54421366000008</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -8244,16 +8253,16 @@
         <v>0.145</v>
       </c>
       <c r="C326">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D326">
-        <v>879.9997151600001</v>
+        <v>886.75304159</v>
       </c>
       <c r="E326">
-        <v>786.77612263</v>
+        <v>836.73036895</v>
       </c>
       <c r="F326">
-        <v>93.22359253000002</v>
+        <v>50.02267264</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -8264,16 +8273,16 @@
         <v>0.145</v>
       </c>
       <c r="C327">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D327">
-        <v>874.15038234</v>
+        <v>882.54491138</v>
       </c>
       <c r="E327">
-        <v>786.77612263</v>
+        <v>837.52492101</v>
       </c>
       <c r="F327">
-        <v>87.37425970999993</v>
+        <v>45.01999037000007</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -8284,16 +8293,16 @@
         <v>0.145</v>
       </c>
       <c r="C328">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D328">
-        <v>867.4195215</v>
+        <v>877.56759459</v>
       </c>
       <c r="E328">
-        <v>786.77612263</v>
+        <v>836.26813924</v>
       </c>
       <c r="F328">
-        <v>80.64339886999994</v>
+        <v>41.29945535000002</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -8304,16 +8313,16 @@
         <v>0.145</v>
       </c>
       <c r="C329">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D329">
-        <v>859.85801896</v>
+        <v>871.90035214</v>
       </c>
       <c r="E329">
-        <v>786.77612263</v>
+        <v>837.15197719</v>
       </c>
       <c r="F329">
-        <v>73.08189632999995</v>
+        <v>34.74837494999997</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -8321,19 +8330,19 @@
         <v>334</v>
       </c>
       <c r="B330">
-        <v>0.15</v>
+        <v>0.145</v>
       </c>
       <c r="C330">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D330">
-        <v>891.81131739</v>
+        <v>865.62824143</v>
       </c>
       <c r="E330">
-        <v>820.74106227</v>
+        <v>838.80561123</v>
       </c>
       <c r="F330">
-        <v>71.07025511999996</v>
+        <v>26.82263020000005</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -8341,19 +8350,19 @@
         <v>335</v>
       </c>
       <c r="B331">
-        <v>0.15</v>
+        <v>0.145</v>
       </c>
       <c r="C331">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D331">
-        <v>892.9520394</v>
+        <v>858.8430269</v>
       </c>
       <c r="E331">
-        <v>787.18636435</v>
+        <v>840.73428772</v>
       </c>
       <c r="F331">
-        <v>105.76567505</v>
+        <v>18.10873918000004</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -8364,16 +8373,16 @@
         <v>0.15</v>
       </c>
       <c r="C332">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D332">
-        <v>893.08922259</v>
+        <v>891.81467916</v>
       </c>
       <c r="E332">
-        <v>782.42763656</v>
+        <v>820.72393217</v>
       </c>
       <c r="F332">
-        <v>110.66158603</v>
+        <v>71.09074698999996</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -8384,16 +8393,16 @@
         <v>0.15</v>
       </c>
       <c r="C333">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D333">
-        <v>892.1802142499999</v>
+        <v>892.76202025</v>
       </c>
       <c r="E333">
-        <v>778.4033752</v>
+        <v>814.8361693000001</v>
       </c>
       <c r="F333">
-        <v>113.7768390499999</v>
+        <v>77.92585094999993</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -8404,16 +8413,16 @@
         <v>0.15</v>
       </c>
       <c r="C334">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D334">
-        <v>890.20953714</v>
+        <v>892.41030412</v>
       </c>
       <c r="E334">
-        <v>778.4033752</v>
+        <v>817.44370908</v>
       </c>
       <c r="F334">
-        <v>111.8061619399999</v>
+        <v>74.96659504000002</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -8424,16 +8433,16 @@
         <v>0.15</v>
       </c>
       <c r="C335">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D335">
-        <v>887.18431299</v>
+        <v>890.92568569</v>
       </c>
       <c r="E335">
-        <v>783.11981136</v>
+        <v>826.83178563</v>
       </c>
       <c r="F335">
-        <v>104.06450163</v>
+        <v>64.09390006000001</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -8444,16 +8453,16 @@
         <v>0.15</v>
       </c>
       <c r="C336">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D336">
-        <v>883.12933065</v>
+        <v>888.42178486</v>
       </c>
       <c r="E336">
-        <v>786.77612263</v>
+        <v>832.7945833700001</v>
       </c>
       <c r="F336">
-        <v>96.35320802000001</v>
+        <v>55.62720148999995</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -8464,16 +8473,16 @@
         <v>0.15</v>
       </c>
       <c r="C337">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D337">
-        <v>878.08222062</v>
+        <v>884.98758324</v>
       </c>
       <c r="E337">
-        <v>786.77612263</v>
+        <v>835.9769924</v>
       </c>
       <c r="F337">
-        <v>91.30609799000001</v>
+        <v>49.01059084000008</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -8484,16 +8493,16 @@
         <v>0.15</v>
       </c>
       <c r="C338">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D338">
-        <v>872.08918877</v>
+        <v>880.7039823600001</v>
       </c>
       <c r="E338">
-        <v>786.77612263</v>
+        <v>836.81038339</v>
       </c>
       <c r="F338">
-        <v>85.31306613999993</v>
+        <v>43.89359897000008</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -8504,16 +8513,16 @@
         <v>0.15</v>
       </c>
       <c r="C339">
-        <v>0.045</v>
+        <v>0.035</v>
       </c>
       <c r="D339">
-        <v>865.20152237</v>
+        <v>875.65217421</v>
       </c>
       <c r="E339">
-        <v>786.77612263</v>
+        <v>835.6003059</v>
       </c>
       <c r="F339">
-        <v>78.42539973999999</v>
+        <v>40.05186831000003</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -8524,16 +8533,16 @@
         <v>0.15</v>
       </c>
       <c r="C340">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D340">
-        <v>857.4729081</v>
+        <v>869.9177049899999</v>
       </c>
       <c r="E340">
-        <v>786.77612263</v>
+        <v>836.6085384100001</v>
       </c>
       <c r="F340">
-        <v>70.69678547000001</v>
+        <v>33.3091665799999</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -8541,19 +8550,19 @@
         <v>345</v>
       </c>
       <c r="B341">
-        <v>0.155</v>
+        <v>0.15</v>
       </c>
       <c r="C341">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D341">
-        <v>890.27281995</v>
+        <v>863.59234895</v>
       </c>
       <c r="E341">
-        <v>820.74106227</v>
+        <v>838.21358761</v>
       </c>
       <c r="F341">
-        <v>69.53175767999994</v>
+        <v>25.37876133999998</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -8561,19 +8570,19 @@
         <v>346</v>
       </c>
       <c r="B342">
-        <v>0.155</v>
+        <v>0.15</v>
       </c>
       <c r="C342">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="D342">
-        <v>891.43180368</v>
+        <v>856.77478932</v>
       </c>
       <c r="E342">
-        <v>787.18636435</v>
+        <v>840.13307317</v>
       </c>
       <c r="F342">
-        <v>104.2454393300001</v>
+        <v>16.64171614999998</v>
       </c>
     </row>
     <row r="343" spans="1:6">
@@ -8584,16 +8593,16 @@
         <v>0.155</v>
       </c>
       <c r="C343">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D343">
-        <v>891.56235139</v>
+        <v>890.27613084</v>
       </c>
       <c r="E343">
-        <v>782.56643839</v>
+        <v>820.7236995</v>
       </c>
       <c r="F343">
-        <v>108.995913</v>
+        <v>69.55243134</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -8604,16 +8613,16 @@
         <v>0.155</v>
       </c>
       <c r="C344">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D344">
-        <v>890.61779089</v>
+        <v>891.19511118</v>
       </c>
       <c r="E344">
-        <v>778.4033752</v>
+        <v>814.79081783</v>
       </c>
       <c r="F344">
-        <v>112.21441569</v>
+        <v>76.40429334999999</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -8624,16 +8633,16 @@
         <v>0.155</v>
       </c>
       <c r="C345">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D345">
-        <v>888.58290575</v>
+        <v>890.80439109</v>
       </c>
       <c r="E345">
-        <v>778.4033752</v>
+        <v>816.77832792</v>
       </c>
       <c r="F345">
-        <v>110.17953055</v>
+        <v>74.02606316999993</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -8644,16 +8653,16 @@
         <v>0.155</v>
       </c>
       <c r="C346">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="D346">
-        <v>885.46718245</v>
+        <v>889.2675355699999</v>
       </c>
       <c r="E346">
-        <v>782.53944302</v>
+        <v>826.10465172</v>
       </c>
       <c r="F346">
-        <v>102.92773943</v>
+        <v>63.16288384999996</v>
       </c>
     </row>
     <row r="347" spans="1:6">
@@ -8664,16 +8673,16 @@
         <v>0.155</v>
       </c>
       <c r="C347">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D347">
-        <v>876.11859315</v>
+        <v>886.69947192</v>
       </c>
       <c r="E347">
-        <v>786.77612263</v>
+        <v>832.05797021</v>
       </c>
       <c r="F347">
-        <v>89.34247052000001</v>
+        <v>54.64150170999994</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -8684,16 +8693,16 @@
         <v>0.155</v>
       </c>
       <c r="C348">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D348">
-        <v>869.97654822</v>
+        <v>883.19287697</v>
       </c>
       <c r="E348">
-        <v>786.77612263</v>
+        <v>835.25908437</v>
       </c>
       <c r="F348">
-        <v>83.20042559000001</v>
+        <v>47.93379260000006</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -8704,16 +8713,16 @@
         <v>0.155</v>
       </c>
       <c r="C349">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D349">
-        <v>862.92702588</v>
+        <v>878.83380927</v>
       </c>
       <c r="E349">
-        <v>786.77612263</v>
+        <v>836.1264738900001</v>
       </c>
       <c r="F349">
-        <v>76.15090324999994</v>
+        <v>42.7073353799999</v>
       </c>
     </row>
     <row r="350" spans="1:6">
@@ -8724,16 +8733,16 @@
         <v>0.155</v>
       </c>
       <c r="C350">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="D350">
-        <v>855.0265536000001</v>
+        <v>873.70955696</v>
       </c>
       <c r="E350">
-        <v>786.77612263</v>
+        <v>834.95871764</v>
       </c>
       <c r="F350">
-        <v>68.25043097000002</v>
+        <v>38.75083931999995</v>
       </c>
     </row>
     <row r="351" spans="1:6">
@@ -8741,19 +8750,19 @@
         <v>355</v>
       </c>
       <c r="B351">
-        <v>0.16</v>
+        <v>0.155</v>
       </c>
       <c r="C351">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D351">
-        <v>888.71988234</v>
+        <v>867.91239645</v>
       </c>
       <c r="E351">
-        <v>820.74106227</v>
+        <v>836.0663798099999</v>
       </c>
       <c r="F351">
-        <v>67.97882006999998</v>
+        <v>31.84601664000002</v>
       </c>
     </row>
     <row r="352" spans="1:6">
@@ -8761,19 +8770,19 @@
         <v>356</v>
       </c>
       <c r="B352">
-        <v>0.16</v>
+        <v>0.155</v>
       </c>
       <c r="C352">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="D352">
-        <v>889.8950306200001</v>
+        <v>861.54122281</v>
       </c>
       <c r="E352">
-        <v>787.18636435</v>
+        <v>837.61432891</v>
       </c>
       <c r="F352">
-        <v>102.7086662700001</v>
+        <v>23.92689389999998</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -8781,19 +8790,19 @@
         <v>357</v>
       </c>
       <c r="B353">
-        <v>0.16</v>
+        <v>0.155</v>
       </c>
       <c r="C353">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D353">
-        <v>890.01512501</v>
+        <v>854.7019051</v>
       </c>
       <c r="E353">
-        <v>782.70824336</v>
+        <v>839.50382542</v>
       </c>
       <c r="F353">
-        <v>107.30688165</v>
+        <v>15.19807967999998</v>
       </c>
     </row>
     <row r="354" spans="1:6">
@@ -8804,16 +8813,16 @@
         <v>0.16</v>
       </c>
       <c r="C354">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D354">
-        <v>889.03017187</v>
+        <v>888.72313559</v>
       </c>
       <c r="E354">
-        <v>778.4033752</v>
+        <v>820.72346041</v>
       </c>
       <c r="F354">
-        <v>110.62679667</v>
+        <v>67.99967517999994</v>
       </c>
     </row>
     <row r="355" spans="1:6">
@@ -8824,16 +8833,16 @@
         <v>0.16</v>
       </c>
       <c r="C355">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D355">
-        <v>886.9256819</v>
+        <v>889.61007136</v>
       </c>
       <c r="E355">
-        <v>778.4033752</v>
+        <v>814.74507916</v>
       </c>
       <c r="F355">
-        <v>108.5223066999999</v>
+        <v>74.86499219999996</v>
       </c>
     </row>
     <row r="356" spans="1:6">
@@ -8844,16 +8853,16 @@
         <v>0.16</v>
       </c>
       <c r="C356">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="D356">
-        <v>883.71382048</v>
+        <v>889.17648046</v>
       </c>
       <c r="E356">
-        <v>781.89130601</v>
+        <v>816.1638799900001</v>
       </c>
       <c r="F356">
-        <v>101.82251447</v>
+        <v>73.01260046999994</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -8864,16 +8873,16 @@
         <v>0.16</v>
       </c>
       <c r="C357">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="D357">
-        <v>879.42614483</v>
+        <v>887.58390671</v>
       </c>
       <c r="E357">
-        <v>786.5748248899999</v>
+        <v>825.42095407</v>
       </c>
       <c r="F357">
-        <v>92.85131994000005</v>
+        <v>62.16295263999996</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -8884,16 +8893,16 @@
         <v>0.16</v>
       </c>
       <c r="C358">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D358">
-        <v>874.10750016</v>
+        <v>884.94906954</v>
       </c>
       <c r="E358">
-        <v>786.77612263</v>
+        <v>831.35894089</v>
       </c>
       <c r="F358">
-        <v>87.33137752999994</v>
+        <v>53.59012865</v>
       </c>
     </row>
     <row r="359" spans="1:6">
@@ -8904,16 +8913,16 @@
         <v>0.16</v>
       </c>
       <c r="C359">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D359">
-        <v>867.81108518</v>
+        <v>881.36879945</v>
       </c>
       <c r="E359">
-        <v>786.77612263</v>
+        <v>834.5739069799999</v>
       </c>
       <c r="F359">
-        <v>81.03496254999993</v>
+        <v>46.79489247000004</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -8924,16 +8933,16 @@
         <v>0.16</v>
       </c>
       <c r="C360">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D360">
-        <v>860.59461931</v>
+        <v>876.93477518</v>
       </c>
       <c r="E360">
-        <v>786.77612263</v>
+        <v>835.47102961</v>
       </c>
       <c r="F360">
-        <v>73.81849667999995</v>
+        <v>41.46374557000001</v>
       </c>
     </row>
     <row r="361" spans="1:6">
@@ -8944,16 +8953,16 @@
         <v>0.16</v>
       </c>
       <c r="C361">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="D361">
-        <v>852.51752134</v>
+        <v>871.74086071</v>
       </c>
       <c r="E361">
-        <v>786.77612263</v>
+        <v>834.3416896</v>
       </c>
       <c r="F361">
-        <v>65.74139871</v>
+        <v>37.39917111</v>
       </c>
     </row>
     <row r="362" spans="1:6">
@@ -8961,19 +8970,19 @@
         <v>366</v>
       </c>
       <c r="B362">
-        <v>0.165</v>
+        <v>0.16</v>
       </c>
       <c r="C362">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D362">
-        <v>887.15193683</v>
+        <v>865.8865358</v>
       </c>
       <c r="E362">
-        <v>820.74106227</v>
+        <v>835.52734435</v>
       </c>
       <c r="F362">
-        <v>66.41087455999991</v>
+        <v>30.35919145000003</v>
       </c>
     </row>
     <row r="363" spans="1:6">
@@ -8981,19 +8990,19 @@
         <v>367</v>
       </c>
       <c r="B363">
-        <v>0.165</v>
+        <v>0.16</v>
       </c>
       <c r="C363">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="D363">
-        <v>888.34094385</v>
+        <v>859.47821173</v>
       </c>
       <c r="E363">
-        <v>787.18636435</v>
+        <v>837.0115047</v>
       </c>
       <c r="F363">
-        <v>101.1545795000001</v>
+        <v>22.46670702999995</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -9001,19 +9010,19 @@
         <v>368</v>
       </c>
       <c r="B364">
-        <v>0.165</v>
+        <v>0.16</v>
       </c>
       <c r="C364">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D364">
-        <v>888.4466086899999</v>
+        <v>852.62912705</v>
       </c>
       <c r="E364">
-        <v>782.85312664</v>
+        <v>838.8534067099999</v>
       </c>
       <c r="F364">
-        <v>105.5934820499999</v>
+        <v>13.77572034000002</v>
       </c>
     </row>
     <row r="365" spans="1:6">
@@ -9024,16 +9033,16 @@
         <v>0.165</v>
       </c>
       <c r="C365">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D365">
-        <v>887.41629934</v>
+        <v>887.15512539</v>
       </c>
       <c r="E365">
-        <v>778.4033752</v>
+        <v>820.7232146600001</v>
       </c>
       <c r="F365">
-        <v>109.01292414</v>
+        <v>66.43191072999991</v>
       </c>
     </row>
     <row r="366" spans="1:6">
@@ -9044,16 +9053,16 @@
         <v>0.165</v>
       </c>
       <c r="C366">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D366">
-        <v>885.236711</v>
+        <v>888.00623564</v>
       </c>
       <c r="E366">
-        <v>778.4033752</v>
+        <v>814.69896611</v>
       </c>
       <c r="F366">
-        <v>106.8333358</v>
+        <v>73.30726952999999</v>
       </c>
     </row>
     <row r="367" spans="1:6">
@@ -9064,16 +9073,16 @@
         <v>0.165</v>
       </c>
       <c r="C367">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="D367">
-        <v>881.92299355</v>
+        <v>887.5258888</v>
       </c>
       <c r="E367">
-        <v>781.16830634</v>
+        <v>815.59516281</v>
       </c>
       <c r="F367">
-        <v>100.75468721</v>
+        <v>71.93072598999993</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -9084,16 +9093,16 @@
         <v>0.165</v>
       </c>
       <c r="C368">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="D368">
-        <v>877.51039733</v>
+        <v>885.8741946</v>
       </c>
       <c r="E368">
-        <v>786.41113478</v>
+        <v>824.77670005</v>
       </c>
       <c r="F368">
-        <v>91.09926255000005</v>
+        <v>61.09749454999996</v>
       </c>
     </row>
     <row r="369" spans="1:6">
@@ -9104,16 +9113,16 @@
         <v>0.165</v>
       </c>
       <c r="C369">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D369">
-        <v>872.04758845</v>
+        <v>883.17017851</v>
       </c>
       <c r="E369">
-        <v>786.77612263</v>
+        <v>830.69437462</v>
       </c>
       <c r="F369">
-        <v>85.27146582</v>
+        <v>52.47580389000007</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -9124,16 +9133,16 @@
         <v>0.165</v>
       </c>
       <c r="C370">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D370">
-        <v>865.59140124</v>
+        <v>879.5153215399999</v>
       </c>
       <c r="E370">
-        <v>786.77612263</v>
+        <v>833.91900092</v>
       </c>
       <c r="F370">
-        <v>78.81527860999995</v>
+        <v>45.59632061999991</v>
       </c>
     </row>
     <row r="371" spans="1:6">
@@ -9144,16 +9153,16 @@
         <v>0.165</v>
       </c>
       <c r="C371">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D371">
-        <v>858.20287265</v>
+        <v>875.00743216</v>
       </c>
       <c r="E371">
-        <v>786.77612263</v>
+        <v>834.84211662</v>
       </c>
       <c r="F371">
-        <v>71.42675001999999</v>
+        <v>40.16531554000005</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -9164,16 +9173,16 @@
         <v>0.165</v>
       </c>
       <c r="C372">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="D372">
-        <v>849.94435574</v>
+        <v>869.74747409</v>
       </c>
       <c r="E372">
-        <v>786.77612263</v>
+        <v>833.86315975</v>
       </c>
       <c r="F372">
-        <v>63.16823310999996</v>
+        <v>35.88431433999995</v>
       </c>
     </row>
     <row r="373" spans="1:6">
@@ -9181,19 +9190,19 @@
         <v>377</v>
       </c>
       <c r="B373">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="C373">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D373">
-        <v>885.5683988</v>
+        <v>863.84262764</v>
       </c>
       <c r="E373">
-        <v>820.74106227</v>
+        <v>834.99300859</v>
       </c>
       <c r="F373">
-        <v>64.82733652999991</v>
+        <v>28.84961905</v>
       </c>
     </row>
     <row r="374" spans="1:6">
@@ -9201,19 +9210,19 @@
         <v>378</v>
       </c>
       <c r="B374">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="C374">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="D374">
-        <v>886.7687485</v>
+        <v>857.40718244</v>
       </c>
       <c r="E374">
-        <v>787.18636435</v>
+        <v>836.40834259</v>
       </c>
       <c r="F374">
-        <v>99.58238415000005</v>
+        <v>20.99883985000008</v>
       </c>
     </row>
     <row r="375" spans="1:6">
@@ -9221,19 +9230,19 @@
         <v>379</v>
       </c>
       <c r="B375">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="C375">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D375">
-        <v>886.85584925</v>
+        <v>850.5617993</v>
       </c>
       <c r="E375">
-        <v>783.00116361</v>
+        <v>838.18822569</v>
       </c>
       <c r="F375">
-        <v>103.85468564</v>
+        <v>12.37357360999999</v>
       </c>
     </row>
     <row r="376" spans="1:6">
@@ -9244,16 +9253,16 @@
         <v>0.17</v>
       </c>
       <c r="C376">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D376">
-        <v>885.77509754</v>
+        <v>885.5715153899999</v>
       </c>
       <c r="E376">
-        <v>778.4033752</v>
+        <v>820.72296218</v>
       </c>
       <c r="F376">
-        <v>107.37172234</v>
+        <v>64.84855320999998</v>
       </c>
     </row>
     <row r="377" spans="1:6">
@@ -9264,16 +9273,16 @@
         <v>0.17</v>
       </c>
       <c r="C377">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D377">
-        <v>883.5148195100001</v>
+        <v>886.38292689</v>
       </c>
       <c r="E377">
-        <v>778.4033752</v>
+        <v>814.65249305</v>
       </c>
       <c r="F377">
-        <v>105.11144431</v>
+        <v>71.73043384000005</v>
       </c>
     </row>
     <row r="378" spans="1:6">
@@ -9284,16 +9293,16 @@
         <v>0.17</v>
       </c>
       <c r="C378">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="D378">
-        <v>880.09344819</v>
+        <v>885.8519305900001</v>
       </c>
       <c r="E378">
-        <v>780.36269309</v>
+        <v>815.06744831</v>
       </c>
       <c r="F378">
-        <v>99.73075510000001</v>
+        <v>70.78448228000002</v>
       </c>
     </row>
     <row r="379" spans="1:6">
@@ -9304,16 +9313,16 @@
         <v>0.17</v>
       </c>
       <c r="C379">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="D379">
-        <v>875.55012834</v>
+        <v>884.13781304</v>
       </c>
       <c r="E379">
-        <v>786.21559961</v>
+        <v>824.16827423</v>
       </c>
       <c r="F379">
-        <v>89.33452872999999</v>
+        <v>59.96953881000002</v>
       </c>
     </row>
     <row r="380" spans="1:6">
@@ -9324,16 +9333,16 @@
         <v>0.17</v>
       </c>
       <c r="C380">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D380">
-        <v>869.93748098</v>
+        <v>881.36245379</v>
       </c>
       <c r="E380">
-        <v>786.77612263</v>
+        <v>830.06145844</v>
       </c>
       <c r="F380">
-        <v>83.16135835</v>
+        <v>51.30099534999999</v>
       </c>
     </row>
     <row r="381" spans="1:6">
@@ -9344,16 +9353,16 @@
         <v>0.17</v>
       </c>
       <c r="C381">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D381">
-        <v>863.31607674</v>
+        <v>877.63252554</v>
       </c>
       <c r="E381">
-        <v>786.77612263</v>
+        <v>833.29216066</v>
       </c>
       <c r="F381">
-        <v>76.53995410999994</v>
+        <v>44.34036487999992</v>
       </c>
     </row>
     <row r="382" spans="1:6">
@@ -9364,16 +9373,16 @@
         <v>0.17</v>
       </c>
       <c r="C382">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D382">
-        <v>855.75033179</v>
+        <v>873.05252977</v>
       </c>
       <c r="E382">
-        <v>786.77612263</v>
+        <v>834.23801169</v>
       </c>
       <c r="F382">
-        <v>68.97420915999999</v>
+        <v>38.81451807999997</v>
       </c>
     </row>
     <row r="383" spans="1:6">
@@ -9384,16 +9393,16 @@
         <v>0.17</v>
       </c>
       <c r="C383">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="D383">
-        <v>847.30558208</v>
+        <v>867.73109985</v>
       </c>
       <c r="E383">
-        <v>786.77612263</v>
+        <v>833.39729315</v>
       </c>
       <c r="F383">
-        <v>60.52945944999999</v>
+        <v>34.33380669999997</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -9401,19 +9410,19 @@
         <v>388</v>
       </c>
       <c r="B384">
-        <v>0.175</v>
+        <v>0.17</v>
       </c>
       <c r="C384">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D384">
-        <v>883.96866679</v>
+        <v>861.78362637</v>
       </c>
       <c r="E384">
-        <v>820.74106227</v>
+        <v>834.46470483</v>
       </c>
       <c r="F384">
-        <v>63.22760452</v>
+        <v>27.31892154000002</v>
       </c>
     </row>
     <row r="385" spans="1:6">
@@ -9421,19 +9430,19 @@
         <v>389</v>
       </c>
       <c r="B385">
-        <v>0.175</v>
+        <v>0.17</v>
       </c>
       <c r="C385">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="D385">
-        <v>885.17763294</v>
+        <v>855.33257208</v>
       </c>
       <c r="E385">
-        <v>787.18636435</v>
+        <v>835.80762964</v>
       </c>
       <c r="F385">
-        <v>97.99126859</v>
+        <v>19.52494244000002</v>
       </c>
     </row>
     <row r="386" spans="1:6">
@@ -9441,19 +9450,19 @@
         <v>390</v>
       </c>
       <c r="B386">
-        <v>0.175</v>
+        <v>0.17</v>
       </c>
       <c r="C386">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D386">
-        <v>885.24187657</v>
+        <v>848.50588006</v>
       </c>
       <c r="E386">
-        <v>783.15242904</v>
+        <v>837.51410054</v>
       </c>
       <c r="F386">
-        <v>102.08944753</v>
+        <v>10.99177952000002</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -9464,16 +9473,16 @@
         <v>0.175</v>
       </c>
       <c r="C387">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D387">
-        <v>884.10547223</v>
+        <v>883.97170386</v>
       </c>
       <c r="E387">
-        <v>778.4033752</v>
+        <v>820.72270196</v>
       </c>
       <c r="F387">
-        <v>105.70209703</v>
+        <v>63.24900190000005</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -9484,16 +9493,16 @@
         <v>0.175</v>
       </c>
       <c r="C388">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D388">
-        <v>881.75881436</v>
+        <v>884.73945585</v>
       </c>
       <c r="E388">
-        <v>778.4033752</v>
+        <v>814.60567596</v>
       </c>
       <c r="F388">
-        <v>103.3554391599999</v>
+        <v>70.13377989000003</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -9504,16 +9513,16 @@
         <v>0.175</v>
       </c>
       <c r="C389">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="D389">
-        <v>878.22391022</v>
+        <v>884.15392014</v>
       </c>
       <c r="E389">
-        <v>779.46607596</v>
+        <v>814.5764425900001</v>
       </c>
       <c r="F389">
-        <v>98.75783425999998</v>
+        <v>69.57747754999991</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -9524,16 +9533,16 @@
         <v>0.175</v>
       </c>
       <c r="C390">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="D390">
-        <v>873.54399566</v>
+        <v>882.37419864</v>
       </c>
       <c r="E390">
-        <v>785.98447034</v>
+        <v>823.5924063</v>
       </c>
       <c r="F390">
-        <v>87.55952531999992</v>
+        <v>58.78179234000004</v>
       </c>
     </row>
     <row r="391" spans="1:6">
@@ -9544,16 +9553,16 @@
         <v>0.175</v>
       </c>
       <c r="C391">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D391">
-        <v>867.77578198</v>
+        <v>879.52561316</v>
       </c>
       <c r="E391">
-        <v>786.77612263</v>
+        <v>829.45766083</v>
       </c>
       <c r="F391">
-        <v>80.99965935</v>
+        <v>50.06795233000003</v>
       </c>
     </row>
     <row r="392" spans="1:6">
@@ -9564,16 +9573,16 @@
         <v>0.175</v>
       </c>
       <c r="C392">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D392">
-        <v>860.98366866</v>
+        <v>875.72062392</v>
       </c>
       <c r="E392">
-        <v>786.77612263</v>
+        <v>832.69141244</v>
       </c>
       <c r="F392">
-        <v>74.20754603</v>
+        <v>43.02921147999996</v>
       </c>
     </row>
     <row r="393" spans="1:6">
@@ -9584,16 +9593,16 @@
         <v>0.175</v>
       </c>
       <c r="C393">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D393">
-        <v>853.2355212799999</v>
+        <v>871.07104641</v>
       </c>
       <c r="E393">
-        <v>786.77612263</v>
+        <v>833.6571829</v>
       </c>
       <c r="F393">
-        <v>66.45939864999991</v>
+        <v>37.41386351000006</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -9604,16 +9613,16 @@
         <v>0.175</v>
       </c>
       <c r="C394">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="D394">
-        <v>844.5997042400001</v>
+        <v>865.6938033599999</v>
       </c>
       <c r="E394">
-        <v>786.77612263</v>
+        <v>832.93876969</v>
       </c>
       <c r="F394">
-        <v>57.82358161000002</v>
+        <v>32.75503366999999</v>
       </c>
     </row>
     <row r="395" spans="1:6">
@@ -9621,19 +9630,19 @@
         <v>399</v>
       </c>
       <c r="B395">
-        <v>0.18</v>
+        <v>0.175</v>
       </c>
       <c r="C395">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D395">
-        <v>882.35212211</v>
+        <v>859.7129955299999</v>
       </c>
       <c r="E395">
-        <v>820.74106227</v>
+        <v>833.94354691</v>
       </c>
       <c r="F395">
-        <v>61.61105983999994</v>
+        <v>25.76944861999993</v>
       </c>
     </row>
     <row r="396" spans="1:6">
@@ -9641,19 +9650,19 @@
         <v>400</v>
       </c>
       <c r="B396">
-        <v>0.18</v>
+        <v>0.175</v>
       </c>
       <c r="C396">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="D396">
-        <v>883.56676728</v>
+        <v>853.2594380199999</v>
       </c>
       <c r="E396">
-        <v>787.18636435</v>
+        <v>835.21173141</v>
       </c>
       <c r="F396">
-        <v>96.38040293000006</v>
+        <v>18.04770660999998</v>
       </c>
     </row>
     <row r="397" spans="1:6">
@@ -9661,19 +9670,19 @@
         <v>401</v>
       </c>
       <c r="B397">
-        <v>0.18</v>
+        <v>0.175</v>
       </c>
       <c r="C397">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D397">
-        <v>883.6037007</v>
+        <v>846.46794644</v>
       </c>
       <c r="E397">
-        <v>783.30699668</v>
+        <v>836.8361765</v>
       </c>
       <c r="F397">
-        <v>100.29670402</v>
+        <v>9.631769940000027</v>
       </c>
     </row>
     <row r="398" spans="1:6">
@@ -9684,16 +9693,16 @@
         <v>0.18</v>
       </c>
       <c r="C398">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D398">
-        <v>882.40631003</v>
+        <v>882.35507187</v>
       </c>
       <c r="E398">
-        <v>778.4033752</v>
+        <v>820.72243441</v>
       </c>
       <c r="F398">
-        <v>104.00293483</v>
+        <v>61.63263745999996</v>
       </c>
     </row>
     <row r="399" spans="1:6">
@@ -9704,16 +9713,16 @@
         <v>0.18</v>
       </c>
       <c r="C399">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D399">
-        <v>879.96748311</v>
+        <v>883.07512176</v>
       </c>
       <c r="E399">
-        <v>778.4033752</v>
+        <v>814.5585330500001</v>
       </c>
       <c r="F399">
-        <v>101.56410791</v>
+        <v>68.51658870999995</v>
       </c>
     </row>
     <row r="400" spans="1:6">
@@ -9724,16 +9733,16 @@
         <v>0.18</v>
       </c>
       <c r="C400">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="D400">
-        <v>876.31308487</v>
+        <v>882.4311735</v>
       </c>
       <c r="E400">
-        <v>778.46949274</v>
+        <v>814.11824999</v>
       </c>
       <c r="F400">
-        <v>97.84359213000005</v>
+        <v>68.31292351000002</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -9744,16 +9753,16 @@
         <v>0.18</v>
       </c>
       <c r="C401">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="D401">
-        <v>871.49063591</v>
+        <v>880.58281617</v>
       </c>
       <c r="E401">
-        <v>785.71350634</v>
+        <v>823.04614254</v>
       </c>
       <c r="F401">
-        <v>85.77712957000006</v>
+        <v>57.53667363</v>
       </c>
     </row>
     <row r="402" spans="1:6">
@@ -9764,16 +9773,16 @@
         <v>0.18</v>
       </c>
       <c r="C402">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D402">
-        <v>865.56107101</v>
+        <v>877.65945053</v>
       </c>
       <c r="E402">
-        <v>786.77612263</v>
+        <v>828.88070843</v>
       </c>
       <c r="F402">
-        <v>78.78494837999995</v>
+        <v>48.77874209999993</v>
       </c>
     </row>
     <row r="403" spans="1:6">
@@ -9784,16 +9793,16 @@
         <v>0.18</v>
       </c>
       <c r="C403">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D403">
-        <v>858.59271217</v>
+        <v>873.77998282</v>
       </c>
       <c r="E403">
-        <v>786.77612263</v>
+        <v>832.11499555</v>
       </c>
       <c r="F403">
-        <v>71.81658954</v>
+        <v>41.66498726999998</v>
       </c>
     </row>
     <row r="404" spans="1:6">
@@ -9804,16 +9813,16 @@
         <v>0.18</v>
       </c>
       <c r="C404">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D404">
-        <v>850.65694354</v>
+        <v>869.06423201</v>
       </c>
       <c r="E404">
-        <v>786.77612263</v>
+        <v>833.09827166</v>
       </c>
       <c r="F404">
-        <v>63.88082091000001</v>
+        <v>35.96596034999993</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -9824,16 +9833,16 @@
         <v>0.18</v>
       </c>
       <c r="C405">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="D405">
-        <v>841.8252042399999</v>
+        <v>863.63806955</v>
       </c>
       <c r="E405">
-        <v>786.77612263</v>
+        <v>832.48805684</v>
       </c>
       <c r="F405">
-        <v>55.04908160999992</v>
+        <v>31.15001270999994</v>
       </c>
     </row>
     <row r="406" spans="1:6">
@@ -9841,19 +9850,19 @@
         <v>410</v>
       </c>
       <c r="B406">
-        <v>0.185</v>
+        <v>0.18</v>
       </c>
       <c r="C406">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D406">
-        <v>880.71812856</v>
+        <v>857.63477212</v>
       </c>
       <c r="E406">
-        <v>820.74106227</v>
+        <v>833.43045766</v>
       </c>
       <c r="F406">
-        <v>59.97706628999993</v>
+        <v>24.20431445999998</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -9861,19 +9870,19 @@
         <v>411</v>
       </c>
       <c r="B407">
-        <v>0.185</v>
+        <v>0.18</v>
       </c>
       <c r="C407">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="D407">
-        <v>881.93530759</v>
+        <v>851.1934998</v>
       </c>
       <c r="E407">
-        <v>787.18636435</v>
+        <v>834.62262413</v>
       </c>
       <c r="F407">
-        <v>94.74894324000002</v>
+        <v>16.57087567000008</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -9881,19 +9890,19 @@
         <v>412</v>
       </c>
       <c r="B408">
-        <v>0.185</v>
+        <v>0.18</v>
       </c>
       <c r="C408">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D408">
-        <v>881.94031574</v>
+        <v>844.45517304</v>
       </c>
       <c r="E408">
-        <v>783.46493849</v>
+        <v>836.15889304</v>
       </c>
       <c r="F408">
-        <v>98.47537724999995</v>
+        <v>8.296280000000024</v>
       </c>
     </row>
     <row r="409" spans="1:6">
@@ -9904,16 +9913,16 @@
         <v>0.185</v>
       </c>
       <c r="C409">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D409">
-        <v>880.6764797</v>
+        <v>880.72098296</v>
       </c>
       <c r="E409">
-        <v>778.4033752</v>
+        <v>820.72215894</v>
       </c>
       <c r="F409">
-        <v>102.2731044999999</v>
+        <v>59.99882402000003</v>
       </c>
     </row>
     <row r="410" spans="1:6">
@@ -9924,16 +9933,16 @@
         <v>0.185</v>
       </c>
       <c r="C410">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D410">
-        <v>878.1395922200001</v>
+        <v>881.38921267</v>
       </c>
       <c r="E410">
-        <v>778.4033752</v>
+        <v>814.5110849500001</v>
       </c>
       <c r="F410">
-        <v>99.73621702000003</v>
+        <v>66.87812771999995</v>
       </c>
     </row>
     <row r="411" spans="1:6">
@@ -9944,16 +9953,16 @@
         <v>0.185</v>
       </c>
       <c r="C411">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="D411">
-        <v>874.35965573</v>
+        <v>880.68301077</v>
       </c>
       <c r="E411">
-        <v>778.4033752</v>
+        <v>813.68934097</v>
       </c>
       <c r="F411">
-        <v>95.95628052999996</v>
+        <v>66.99366980000002</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -9964,16 +9973,16 @@
         <v>0.185</v>
       </c>
       <c r="C412">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="D412">
-        <v>869.3886631399999</v>
+        <v>878.76316478</v>
       </c>
       <c r="E412">
-        <v>785.3979044</v>
+        <v>822.52682041</v>
       </c>
       <c r="F412">
-        <v>83.99075873999993</v>
+        <v>56.23634436999998</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -9984,16 +9993,16 @@
         <v>0.185</v>
       </c>
       <c r="C413">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D413">
-        <v>863.29190518</v>
+        <v>875.76384961</v>
       </c>
       <c r="E413">
-        <v>786.77612263</v>
+        <v>828.32856513</v>
       </c>
       <c r="F413">
-        <v>76.51578254999993</v>
+        <v>47.43528447999995</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -10004,16 +10013,16 @@
         <v>0.185</v>
       </c>
       <c r="C414">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D414">
-        <v>856.14172129</v>
+        <v>871.8111497800001</v>
       </c>
       <c r="E414">
-        <v>786.77612263</v>
+        <v>831.5613442</v>
       </c>
       <c r="F414">
-        <v>69.36559865999993</v>
+        <v>40.24980558000004</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -10024,16 +10033,16 @@
         <v>0.185</v>
       </c>
       <c r="C415">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D415">
-        <v>848.0130785600001</v>
+        <v>867.03365129</v>
       </c>
       <c r="E415">
-        <v>786.77612263</v>
+        <v>832.56008447</v>
       </c>
       <c r="F415">
-        <v>61.23695593000002</v>
+        <v>34.47356681999997</v>
       </c>
     </row>
     <row r="416" spans="1:6">
@@ -10044,16 +10053,16 @@
         <v>0.185</v>
       </c>
       <c r="C416">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="D416">
-        <v>838.9805446399999</v>
+        <v>861.56686734</v>
       </c>
       <c r="E416">
-        <v>786.77612263</v>
+        <v>832.04554664</v>
       </c>
       <c r="F416">
-        <v>52.20442200999992</v>
+        <v>29.52132070000005</v>
       </c>
     </row>
     <row r="417" spans="1:6">
@@ -10061,19 +10070,19 @@
         <v>421</v>
       </c>
       <c r="B417">
-        <v>0.19</v>
+        <v>0.185</v>
       </c>
       <c r="C417">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D417">
-        <v>879.0660319900001</v>
+        <v>855.55363161</v>
       </c>
       <c r="E417">
-        <v>820.74106227</v>
+        <v>832.92619668</v>
       </c>
       <c r="F417">
-        <v>58.32496972000001</v>
+        <v>22.62743493000005</v>
       </c>
     </row>
     <row r="418" spans="1:6">
@@ -10081,19 +10090,19 @@
         <v>422</v>
       </c>
       <c r="B418">
-        <v>0.19</v>
+        <v>0.185</v>
       </c>
       <c r="C418">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="D418">
-        <v>880.28238512</v>
+        <v>849.1411668</v>
       </c>
       <c r="E418">
-        <v>787.18636435</v>
+        <v>834.04193559</v>
       </c>
       <c r="F418">
-        <v>93.09602077</v>
+        <v>15.09923120999997</v>
       </c>
     </row>
     <row r="419" spans="1:6">
@@ -10101,19 +10110,19 @@
         <v>423</v>
       </c>
       <c r="B419">
-        <v>0.19</v>
+        <v>0.185</v>
       </c>
       <c r="C419">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D419">
-        <v>880.25069481</v>
+        <v>842.47527688</v>
       </c>
       <c r="E419">
-        <v>783.62632393</v>
+        <v>835.48599385</v>
       </c>
       <c r="F419">
-        <v>96.62437088000001</v>
+        <v>6.989283030000024</v>
       </c>
     </row>
     <row r="420" spans="1:6">
@@ -10124,16 +10133,16 @@
         <v>0.19</v>
       </c>
       <c r="C420">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D420">
-        <v>878.91482809</v>
+        <v>879.06878277</v>
       </c>
       <c r="E420">
-        <v>778.4033752</v>
+        <v>820.7218752</v>
       </c>
       <c r="F420">
-        <v>100.51145289</v>
+        <v>58.34690756999998</v>
       </c>
     </row>
     <row r="421" spans="1:6">
@@ -10144,16 +10153,16 @@
         <v>0.19</v>
       </c>
       <c r="C421">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D421">
-        <v>876.27388787</v>
+        <v>879.68100599</v>
       </c>
       <c r="E421">
-        <v>778.4033752</v>
+        <v>814.4633542399999</v>
       </c>
       <c r="F421">
-        <v>97.87051266999993</v>
+        <v>65.21765175000007</v>
       </c>
     </row>
     <row r="422" spans="1:6">
@@ -10164,16 +10173,16 @@
         <v>0.19</v>
       </c>
       <c r="C422">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="D422">
-        <v>872.36228485</v>
+        <v>878.90875849</v>
       </c>
       <c r="E422">
-        <v>778.4033752</v>
+        <v>813.2865233700001</v>
       </c>
       <c r="F422">
-        <v>93.95890965000001</v>
+        <v>65.62223511999991</v>
       </c>
     </row>
     <row r="423" spans="1:6">
@@ -10184,16 +10193,16 @@
         <v>0.19</v>
       </c>
       <c r="C423">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="D423">
-        <v>867.23666934</v>
+        <v>876.91478594</v>
       </c>
       <c r="E423">
-        <v>785.03221812</v>
+        <v>822.0320458</v>
       </c>
       <c r="F423">
-        <v>82.20445122000001</v>
+        <v>54.88274014000001</v>
       </c>
     </row>
     <row r="424" spans="1:6">
@@ -10204,16 +10213,16 @@
         <v>0.19</v>
       </c>
       <c r="C424">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D424">
-        <v>860.9668183</v>
+        <v>873.83880091</v>
       </c>
       <c r="E424">
-        <v>786.77612263</v>
+        <v>827.79941353</v>
       </c>
       <c r="F424">
-        <v>74.19069566999997</v>
+        <v>46.03938737999999</v>
       </c>
     </row>
     <row r="425" spans="1:6">
@@ -10224,16 +10233,16 @@
         <v>0.19</v>
       </c>
       <c r="C425">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D425">
-        <v>853.6291830599999</v>
+        <v>869.8148861</v>
       </c>
       <c r="E425">
-        <v>786.77612263</v>
+        <v>831.02907286</v>
       </c>
       <c r="F425">
-        <v>66.85306042999991</v>
+        <v>38.78581323999992</v>
       </c>
     </row>
     <row r="426" spans="1:6">
@@ -10244,16 +10253,16 @@
         <v>0.19</v>
       </c>
       <c r="C426">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D426">
-        <v>845.30238373</v>
+        <v>864.9812392600001</v>
       </c>
       <c r="E426">
-        <v>786.77612263</v>
+        <v>832.04157256</v>
       </c>
       <c r="F426">
-        <v>58.52626109999994</v>
+        <v>32.93966670000009</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -10264,16 +10273,16 @@
         <v>0.19</v>
       </c>
       <c r="C427">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="D427">
-        <v>836.06416637</v>
+        <v>859.4837221</v>
       </c>
       <c r="E427">
-        <v>786.77612263</v>
+        <v>831.82131777</v>
       </c>
       <c r="F427">
-        <v>49.28804373999992</v>
+        <v>27.66240433000007</v>
       </c>
     </row>
     <row r="428" spans="1:6">
@@ -10281,19 +10290,19 @@
         <v>432</v>
       </c>
       <c r="B428">
-        <v>0.195</v>
+        <v>0.19</v>
       </c>
       <c r="C428">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D428">
-        <v>877.39516045</v>
+        <v>853.47495195</v>
       </c>
       <c r="E428">
-        <v>820.74106227</v>
+        <v>832.43138827</v>
       </c>
       <c r="F428">
-        <v>56.65409818000001</v>
+        <v>21.04356368000003</v>
       </c>
     </row>
     <row r="429" spans="1:6">
@@ -10301,19 +10310,19 @@
         <v>433</v>
       </c>
       <c r="B429">
-        <v>0.195</v>
+        <v>0.19</v>
       </c>
       <c r="C429">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="D429">
-        <v>878.60711768</v>
+        <v>847.10954279</v>
       </c>
       <c r="E429">
-        <v>787.18636435</v>
+        <v>833.47099045</v>
       </c>
       <c r="F429">
-        <v>91.42075333000003</v>
+        <v>13.63855233999993</v>
       </c>
     </row>
     <row r="430" spans="1:6">
@@ -10321,19 +10330,19 @@
         <v>434</v>
       </c>
       <c r="B430">
-        <v>0.195</v>
+        <v>0.19</v>
       </c>
       <c r="C430">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D430">
-        <v>878.53379345</v>
+        <v>842.8625087200001</v>
       </c>
       <c r="E430">
-        <v>783.79121889</v>
+        <v>834.82056977</v>
       </c>
       <c r="F430">
-        <v>94.74257455999998</v>
+        <v>8.041938950000031</v>
       </c>
     </row>
     <row r="431" spans="1:6">
@@ -10344,16 +10353,16 @@
         <v>0.195</v>
       </c>
       <c r="C431">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D431">
-        <v>877.12018309</v>
+        <v>877.3977991100001</v>
       </c>
       <c r="E431">
-        <v>778.4033752</v>
+        <v>820.7215830599999</v>
       </c>
       <c r="F431">
-        <v>98.71680788999993</v>
+        <v>56.67621605000011</v>
       </c>
     </row>
     <row r="432" spans="1:6">
@@ -10364,16 +10373,16 @@
         <v>0.195</v>
       </c>
       <c r="C432">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D432">
-        <v>874.36909485</v>
+        <v>877.9497694299999</v>
       </c>
       <c r="E432">
-        <v>778.4033752</v>
+        <v>814.41536609</v>
       </c>
       <c r="F432">
-        <v>95.96571964999998</v>
+        <v>63.53440333999993</v>
       </c>
     </row>
     <row r="433" spans="1:6">
@@ -10384,16 +10393,16 @@
         <v>0.195</v>
       </c>
       <c r="C433">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="D433">
-        <v>870.31961067</v>
+        <v>877.10775359</v>
       </c>
       <c r="E433">
-        <v>778.4033752</v>
+        <v>813.00297238</v>
       </c>
       <c r="F433">
-        <v>91.91623546999995</v>
+        <v>64.10478121000006</v>
       </c>
     </row>
     <row r="434" spans="1:6">
@@ -10404,16 +10413,16 @@
         <v>0.195</v>
       </c>
       <c r="C434">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="D434">
-        <v>865.03322203</v>
+        <v>875.03727181</v>
       </c>
       <c r="E434">
-        <v>784.61026708</v>
+        <v>821.55967272</v>
       </c>
       <c r="F434">
-        <v>80.42295495000008</v>
+        <v>53.47759909000001</v>
       </c>
     </row>
     <row r="435" spans="1:6">
@@ -10424,16 +10433,16 @@
         <v>0.195</v>
       </c>
       <c r="C435">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D435">
-        <v>858.58431989</v>
+        <v>871.88442234</v>
       </c>
       <c r="E435">
-        <v>786.77612263</v>
+        <v>827.29163825</v>
       </c>
       <c r="F435">
-        <v>71.80819725999993</v>
+        <v>44.59278409000001</v>
       </c>
     </row>
     <row r="436" spans="1:6">
@@ -10444,16 +10453,16 @@
         <v>0.195</v>
       </c>
       <c r="C436">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D436">
-        <v>851.05356202</v>
+        <v>867.79220819</v>
       </c>
       <c r="E436">
-        <v>786.77612263</v>
+        <v>830.5169620200001</v>
       </c>
       <c r="F436">
-        <v>64.27743938999993</v>
+        <v>37.27524616999995</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -10464,16 +10473,16 @@
         <v>0.195</v>
       </c>
       <c r="C437">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D437">
-        <v>842.52329391</v>
+        <v>862.90936971</v>
       </c>
       <c r="E437">
-        <v>786.77612263</v>
+        <v>831.5418264899999</v>
       </c>
       <c r="F437">
-        <v>55.74717127999998</v>
+        <v>31.36754322000002</v>
       </c>
     </row>
     <row r="438" spans="1:6">
@@ -10484,16 +10493,16 @@
         <v>0.195</v>
       </c>
       <c r="C438">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="D438">
-        <v>833.07448963</v>
+        <v>857.39279578</v>
       </c>
       <c r="E438">
-        <v>786.77612263</v>
+        <v>831.82131784</v>
       </c>
       <c r="F438">
-        <v>46.29836699999998</v>
+        <v>25.57147794000002</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -10501,19 +10510,19 @@
         <v>443</v>
       </c>
       <c r="B439">
-        <v>0.2</v>
+        <v>0.195</v>
       </c>
       <c r="C439">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D439">
-        <v>875.70482341</v>
+        <v>851.40486923</v>
       </c>
       <c r="E439">
-        <v>820.74106227</v>
+        <v>831.94654679</v>
       </c>
       <c r="F439">
-        <v>54.96376113999997</v>
+        <v>19.45832244000007</v>
       </c>
     </row>
     <row r="440" spans="1:6">
@@ -10521,19 +10530,19 @@
         <v>444</v>
       </c>
       <c r="B440">
-        <v>0.2</v>
+        <v>0.195</v>
       </c>
       <c r="C440">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="D440">
-        <v>876.90860449</v>
+        <v>845.10639799</v>
       </c>
       <c r="E440">
-        <v>787.18636435</v>
+        <v>832.91085791</v>
       </c>
       <c r="F440">
-        <v>89.72224014000005</v>
+        <v>12.19554008</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -10541,19 +10550,19 @@
         <v>445</v>
       </c>
       <c r="B441">
-        <v>0.2</v>
+        <v>0.195</v>
       </c>
       <c r="C441">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D441">
-        <v>876.78854702</v>
+        <v>844.3316899</v>
       </c>
       <c r="E441">
-        <v>783.9596844500001</v>
+        <v>834.16512455</v>
       </c>
       <c r="F441">
-        <v>92.82886256999996</v>
+        <v>10.16656535000004</v>
       </c>
     </row>
     <row r="442" spans="1:6">
@@ -10564,16 +10573,16 @@
         <v>0.2</v>
       </c>
       <c r="C442">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D442">
-        <v>875.2913525</v>
+        <v>875.70734125</v>
       </c>
       <c r="E442">
-        <v>778.4033752</v>
+        <v>820.72128163</v>
       </c>
       <c r="F442">
-        <v>96.88797729999999</v>
+        <v>54.98605961999999</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -10584,16 +10593,16 @@
         <v>0.2</v>
       </c>
       <c r="C443">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D443">
-        <v>872.42391573</v>
+        <v>876.19476142</v>
       </c>
       <c r="E443">
-        <v>778.4033752</v>
+        <v>814.36714832</v>
       </c>
       <c r="F443">
-        <v>94.02054052999995</v>
+        <v>61.82761310000001</v>
       </c>
     </row>
     <row r="444" spans="1:6">
@@ -10604,16 +10613,16 @@
         <v>0.2</v>
       </c>
       <c r="C444">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="D444">
-        <v>868.23025033</v>
+        <v>875.27934627</v>
       </c>
       <c r="E444">
-        <v>778.4033752</v>
+        <v>812.9886550799999</v>
       </c>
       <c r="F444">
-        <v>89.82687512999996</v>
+        <v>62.29069119000008</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -10624,16 +10633,16 @@
         <v>0.2</v>
       </c>
       <c r="C445">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="D445">
-        <v>862.77686595</v>
+        <v>873.13027623</v>
       </c>
       <c r="E445">
-        <v>784.12503616</v>
+        <v>821.10778498</v>
       </c>
       <c r="F445">
-        <v>78.65182978999997</v>
+        <v>52.02249125000003</v>
       </c>
     </row>
     <row r="446" spans="1:6">
@@ -10644,16 +10653,16 @@
         <v>0.2</v>
       </c>
       <c r="C446">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="D446">
-        <v>856.14289573</v>
+        <v>869.9009837</v>
       </c>
       <c r="E446">
-        <v>786.77612263</v>
+        <v>826.80381101</v>
       </c>
       <c r="F446">
-        <v>69.36677309999993</v>
+        <v>43.09717268999998</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -10664,16 +10673,16 @@
         <v>0.2</v>
       </c>
       <c r="C447">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="D447">
-        <v>848.4132992900001</v>
+        <v>865.7444342</v>
       </c>
       <c r="E447">
-        <v>786.77612263</v>
+        <v>830.02394636</v>
       </c>
       <c r="F447">
-        <v>61.63717666000002</v>
+        <v>35.72048784000003</v>
       </c>
     </row>
     <row r="448" spans="1:6">
@@ -10684,16 +10693,16 @@
         <v>0.2</v>
       </c>
       <c r="C448">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="D448">
-        <v>839.67421932</v>
+        <v>860.82092191</v>
       </c>
       <c r="E448">
-        <v>786.77612263</v>
+        <v>831.06006272</v>
       </c>
       <c r="F448">
-        <v>52.89809668999999</v>
+        <v>29.76085919000002</v>
       </c>
     </row>
     <row r="449" spans="1:6">
@@ -10704,16 +10713,76 @@
         <v>0.2</v>
       </c>
       <c r="C449">
+        <v>0.035</v>
+      </c>
+      <c r="D449">
+        <v>855.29897196</v>
+      </c>
+      <c r="E449">
+        <v>831.8213177600001</v>
+      </c>
+      <c r="F449">
+        <v>23.47765419999996</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6">
+      <c r="A450" t="s">
+        <v>454</v>
+      </c>
+      <c r="B450">
+        <v>0.2</v>
+      </c>
+      <c r="C450">
+        <v>0.04</v>
+      </c>
+      <c r="D450">
+        <v>849.35031626</v>
+      </c>
+      <c r="E450">
+        <v>831.82131788</v>
+      </c>
+      <c r="F450">
+        <v>17.52899837999996</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6">
+      <c r="A451" t="s">
+        <v>455</v>
+      </c>
+      <c r="B451">
+        <v>0.2</v>
+      </c>
+      <c r="C451">
+        <v>0.045</v>
+      </c>
+      <c r="D451">
+        <v>843.14009417</v>
+      </c>
+      <c r="E451">
+        <v>832.36239719</v>
+      </c>
+      <c r="F451">
+        <v>10.77769697999997</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6">
+      <c r="A452" t="s">
+        <v>456</v>
+      </c>
+      <c r="B452">
+        <v>0.2</v>
+      </c>
+      <c r="C452">
         <v>0.05</v>
       </c>
-      <c r="D449">
-        <v>830.0099119</v>
-      </c>
-      <c r="E449">
-        <v>786.77612263</v>
-      </c>
-      <c r="F449">
-        <v>43.23378926999999</v>
+      <c r="D452">
+        <v>845.7744805</v>
+      </c>
+      <c r="E452">
+        <v>833.5216534800001</v>
+      </c>
+      <c r="F452">
+        <v>12.25282701999993</v>
       </c>
     </row>
   </sheetData>
